--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD91"/>
+  <dimension ref="A1:AD60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,35 +583,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>794532662074117</t>
+          <t>794934231327542</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GMK-000997</t>
+          <t>ME6-000970</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KZZI GAMING KEYBOARD K75 PRO RHINE COLOR MOMENT LINEAR SWITCH RGB MULTI-MODES EN/TH (GMK-000997)</t>
+          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3499</v>
+        <v>299</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3499</v>
+        <v>299</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ready_to_ship</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -631,18 +631,18 @@
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>สิรีธร วชิรปราการสกุล</t>
+          <t>บริษัท เอเชี่ยนแอร์โรสเปซเซอร์วิส จำกัด</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>125/8 ถนนสวรรคโลก ดุสิต</t>
+          <t>65/198 อาคารชำนาญเพ็ญชาติบิสเนสเซ็นเตอร์ ชั้นที่ 23 ถนนพระราม 9 แขวงห้วยขวาง</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ดุสิต/ Dusit</t>
+          <t>ห้วยขวาง/ Huai Khwang</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -652,26 +652,30 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>10300</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr"/>
+          <t>10310</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0105546033311</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>660818557555</t>
+          <t>66026430740</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>สิรีธร วชิรปราการสกุล</t>
+          <t>บุญชัย พจนาสมสมาน</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>3499</v>
+        <v>299</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>23 Dec 2023 00:32</t>
+          <t>24 Dec 2023 00:10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -680,42 +684,42 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>125/8 ถนนสวรรคโลก ดุสิต</t>
+          <t>65/198 อาคารชำนาญเพ็ญชาติบิสเนสเซ็นเตอร์ ชั้นที่ 23 ถนนพระราม 9 แขวงห้วยขวาง</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>794535093906825</t>
+          <t>794945821778234</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SP2-001778</t>
+          <t>MS4-000939</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HP 682 Black Original Ink Cartridge / 3YM77AA SP2-001778</t>
+          <t>SANDISK SDSSDE30 Portable SSD 1TB (Read speed up to 800MB/s,) MS4-000939</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>390</v>
+        <v>2290</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>780</v>
+        <v>2290</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -735,91 +739,91 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>จิรายุทธ เมธาวัชรวงศ์</t>
+          <t>พตท. กฤษฏิ์พันธุ์ ล่ำภากร</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>49/1 หมู่ 6 ถนนชูพันธ์ · ควนลัง/ Khuan Lang</t>
+          <t>หมู่บ้านเดอะคลัสเตอร์วิลล์ 2 เลขที่ 109/60 ซอย 4 บางขุนกอง</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>หาดใหญ่/ Hat Yai</t>
+          <t>บางกรวย/ Bang Kruai</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>สงขลา/ Songkhla</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>90110</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>660896559984</t>
+          <t>660874854442</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Vikky Ivy</t>
+          <t>Gritphan Lumpakorn</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>780</v>
+        <v>2290</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>23 Dec 2023 01:04</t>
+          <t>24 Dec 2023 00:59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>49/1 หมู่ 6 ถนนชูพันธ์ · ควนลัง/ Khuan Lang</t>
+          <t>หมู่บ้านเดอะคลัสเตอร์วิลล์ 2 เลขที่ 109/60 ซอย 4 บางขุนกอง</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>794550035236904</t>
+          <t>794960498511360</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NWW-000590</t>
+          <t>MS2-000917</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASUS PCE-AX3000 Dual Band PCI-E WiFi 6 (802.11ax) wifi6 PCI-E adapter (BOX) Extendable router NWW-000590</t>
+          <t>KINGSTON Kyson DTKN USB A 32GB/5Y MS2-000917</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>990</v>
+        <v>199</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>990</v>
+        <v>199</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>delivered</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -839,95 +843,91 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ณรงค์ฤทธิ์   ห้อยสังวาลย์LZ</t>
+          <t>Mikhail Khalizev</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2/200 ร้านขายต้นไม้ ถ.บ้านปากแรต16 ต.บ้านโป่ง อ.บ้านโป่ง · บ้านโป่ง/ Ban Pong</t>
+          <t>Allamanda 3 Condominium, Ground floor Unit 3130 · เชิงทะเล/ Choeng Thale</t>
         </is>
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>บ้านโป่ง/ Ban Pong</t>
+          <t>ถลาง/ Thalang</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ราชบุรี/ Ratchaburi</t>
+          <t>ภูเก็ต/ Phuket</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>70110</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ภ ถ   ้ท ทื ้ภภถภภถ ถภ้ะถภถ ถภ  ะื  ท  ัถ้้ภั ภ ่    ภภัท้ะภ้ภภภ้ั ถ   ภภภ  ถ ภ ะืภะ ภถะ ถ   ภท    ถภ้ภงงภ ภภ   ภ ภถภภะ้ะภภ้ภภภ้ภ้้ะะัื้ ้ภ้้    ะทะถภ ท ภภ้ภื ถภ ััภภืทท ภ ้ภ ะถ  ้้ถ้ ททภภื ภ ทะาภถ  ถภภ ถถภ้ถภ ภทภื้ภ ืภธงภัถ ถภภะภ ภ ภภภ้ภัภมีทภืถถธงทททภภถภ ้ ภถถนน ภภ ถถภทถถภถภภถะถ ภภ ถ การทะ </t>
-        </is>
-      </c>
+          <t>83110</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>660995287375</t>
+          <t>660629478177</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>ณรงค์ฤทธิ์ ห้อยสังวาลย์</t>
+          <t>Mikhail Khalizev</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>990</v>
+        <v>199</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>23 Dec 2023 01:50</t>
+          <t>24 Dec 2023 05:48</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2/200 ร้านขายต้นไม้ ถ.บ้านปากแรต16 ต.บ้านโป่ง อ.บ้านโป่ง · บ้านโป่ง/ Ban Pong</t>
+          <t>Allamanda 3 Condominium, Ground floor Unit 3130 · เชิงทะเล/ Choeng Thale</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>794563418136110</t>
+          <t>794964650322439</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PR5-000548</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CANON PIXMA G3010 ปริ้นเตอร์อิ๊งค์เจ็ต(PR5-000548) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3450</v>
+        <v>1860</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>3450</v>
+        <v>1860</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ready_to_ship</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -947,95 +947,91 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>น.ส.พัทธนันท์ คำสามารถ</t>
+          <t>กฤติพงษ์ รักพานิชมณี</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>140 หมู่ที่ 5 หมู่บ้าน นันทจันทร์ ต.นากลาง  อ.นากลาง จ.หนองบัวลำภู(บ้านสองชั้นอยู่เยื้องกับรร.สงวนศึกษา)0830335859</t>
+          <t>111/37 หมู่ที่ 14 ปันนา3เรสชิเดนท์ ห้อง419 ซ.7 ถ.สุเทพ ต.สุเทพ</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>นากลาง/ Na Klang</t>
+          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>หนองบัวลำภู/ Nongbua Lamphu</t>
+          <t>เชียงใหม่/ Chiang Mai</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>39170</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>1411400030204</t>
-        </is>
-      </c>
+          <t>50200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>660830335859</t>
+          <t>660869322999</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>พัทธนันท์ คำสามารถ</t>
+          <t>กฤติพงษ์ รักพานิชมณี</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>3450</v>
+        <v>1860</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>23 Dec 2023 04:13</t>
+          <t>24 Dec 2023 05:32</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>140 หมู่ที่ 5 หมู่บ้าน นันทจันทร์ ต.นากลาง  อ.นากลาง จ.หนองบัวลำภู(บ้านสองชั้นอยู่เยื้องกับรร.สงวนศึกษา)0830335859</t>
+          <t>111/37 หมู่ที่ 14 ปันนา3เรสชิเดนท์ ห้อง419 ซ.7 ถ.สุเทพ ต.สุเทพ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>794569606130505</t>
+          <t>794967084728279</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MS2-000960</t>
+          <t>CU2-000471</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen1 DataTraveler Exodia Onyx MS2-000960</t>
+          <t>AMD RYZEN 5 4600G 3.7GHz (6Cores/12Threads) AM4 (3Y) CU2-000471</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>3690</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>135</v>
+        <v>3690</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1055,91 +1051,91 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>จิรวัฒน์ ปิยฉัตรโรจน์</t>
+          <t>วินัย พรมบุญ</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>ร้านเอกรส 612-614 ถ.ราษฏรดำริ ต.หน้าเมือง</t>
+          <t>26/12 คอนโดเทเวศน์ ชั้น 1 ซ.นามบัญญัติ แขวงบางขุ่นพรหม</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>เมืองปราจีนบุรี/ Mueang Prachin Buri</t>
+          <t>พระนคร/ Phra Nakhon</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>ปราจีนบุรี/ Prachin Buri</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>660865133809</t>
+          <t>660647876435</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Jirawat Piyachattaroj</t>
+          <t>Mahiro LW</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>135</v>
+        <v>3690</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>23 Dec 2023 05:27</t>
+          <t>24 Dec 2023 06:29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ร้านเอกรส 612-614 ถ.ราษฏรดำริ ต.หน้าเมือง</t>
+          <t>26/12 คอนโดเทเวศน์ ชั้น 1 ซ.นามบัญญัติ แขวงบางขุ่นพรหม</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>794602239090160</t>
+          <t>795000400748860</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>ME6-000877</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
+          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 128GB, 100/85MB/s ME6-000877</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>295</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>600</v>
+        <v>295</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1159,51 +1155,47 @@
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>อภิชาติ ใจดี</t>
+          <t>Jariyaporn Breuel</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>216หมู่ 9  ต.ดอกคำใต้</t>
+          <t>252 mu 12 Ban Thung Seng Thong Tambon Waeng</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ดอกคำใต้/ Dok Khamtai</t>
+          <t>โพนทอง/ Phon Thong</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>พะเยา/ Phayao</t>
+          <t>ร้อยเอ็ด/ Roi Et</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56120</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0563563000803</t>
-        </is>
-      </c>
+          <t>45110</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>660954522224</t>
+          <t>660929814561</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Apichart Jaidee</t>
+          <t>Jariyaporn Breuel</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>600</v>
+        <v>295</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>23 Dec 2023 08:41</t>
+          <t>24 Dec 2023 08:33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -1212,35 +1204,35 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>216หมู่ 9  ต.ดอกคำใต้</t>
+          <t>252 mu 12 Ban Thung Seng Thong Tambon Waeng</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>794613251964015</t>
+          <t>795001246312124</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>ME6-000916</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
+          <t>KINGSTON MicroSD Canvas GO Plus 64GB 170/70MB/s ME6-000916</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -1267,88 +1259,84 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>ชูชาติ หฤทัยภูมิ</t>
+          <t>Oliver Bohmlander</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>69 ม.12 ต.ข่องสาริกา</t>
+          <t>55/3 Village No. 5 Klong Rang Na mom · นาหม่อม/ Na Mom</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>พัฒนานิคม/ Phatthana Nikhom</t>
+          <t>นาหม่อม/ Na Mom</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>ลพบุรี/ Lopburi</t>
+          <t>สงขลา/ Songkhla</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>15220</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0163560000202</t>
-        </is>
-      </c>
+          <t>90310</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>660956636454</t>
+          <t>660618643392</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>ชูชาติ หฤทัยภูมิ</t>
+          <t>618643392</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>23 Dec 2023 09:23</t>
+          <t>24 Dec 2023 08:53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>69 ม.12 ต.ข่องสาริกา</t>
+          <t>55/3 Village No. 5 Klong Rang Na mom · นาหม่อม/ Na Mom</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>794631412561828</t>
+          <t>795040470960074</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ME6-000876</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>155</v>
+        <v>1860</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>310</v>
+        <v>1860</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -1375,84 +1363,84 @@
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>อรุณ  ชาญฉลาด</t>
+          <t>ว่าที่ร้อยตรีทิวากร ทุมมา</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>32/372ม.6ต.คลองหนึ่ง อ.คลองหลวง จ.ปทุมธานี เชียงกงรังสิต ซ.6</t>
+          <t>23 หมู่ที่ 4 · นาบินหลา/ Na Bin La</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>คลองหลวง/ Khlong Luang</t>
+          <t>เมืองตรัง/ Mueang Trang</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
+          <t>ตรัง/ Trang</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>92170</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>660816102219</t>
+          <t>660610699016</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>อรุณ  ชาญฉลาด</t>
+          <t>0970132826</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>310</v>
+        <v>1860</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>23 Dec 2023 09:45</t>
+          <t>24 Dec 2023 10:54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
-        <v>34</v>
+        <v>80.67</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>32/372ม.6ต.คลองหนึ่ง อ.คลองหลวง จ.ปทุมธานี เชียงกงรังสิต ซ.6</t>
+          <t>23 หมู่ที่ 4 · นาบินหลา/ Na Bin La</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>794636602123023</t>
+          <t>795057611462381</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>IP4-002000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+          <t>LOGITECH SIGNATURE M650 WIRELESS MOUSE ROSE (1Y) IP4-002000</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>279</v>
+        <v>869</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>279</v>
+        <v>869</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -1479,18 +1467,18 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>รัตนา  หวังศิริสมบัติ</t>
+          <t>ศิริเดือน พลับประสิทธิ์</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>15 ซอยเทอดไท71. ถนนเทอดไท</t>
+          <t>171/110 มบ. ทัศนีย์ ซ.6 ซ. พุทธบูชา 39แยก1-1 ถ. พุทธบูชา แขวงบางมด</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ภาษีเจริญ/ Phasi Charoen</t>
+          <t>ทุ่งครุ/ Thung Khru</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1500,70 +1488,70 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>660859041932</t>
+          <t>660863642948</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>รัตนา  หวังศิริสมบัติ</t>
+          <t>ศิริเดือน พลับประสิทธิ์</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>279</v>
+        <v>869</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>23 Dec 2023 09:56</t>
+          <t>24 Dec 2023 11:05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>15 ซอยเทอดไท71. ถนนเทอดไท</t>
+          <t>171/110 มบ. ทัศนีย์ ซ.6 ซ. พุทธบูชา 39แยก1-1 ถ. พุทธบูชา แขวงบางมด</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>794637213694558</t>
+          <t>795079830574423</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SP2-1610+SP2-1611+SP2-1612+SP2-1613</t>
+          <t>ME6-000876</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CANON Ink Bottle GI-790BK,C,M,Y (เซท 4 สี) หมึกพิมพ์ (SP2-1610+SP2-1611+SP2-1612+SP2-1613) SP2-1610+SP2-1611+SP2-1612+SP2-1613</t>
+          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1000</v>
+        <v>155</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>155</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1583,47 +1571,47 @@
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>เชนณี ยุ่นฉลาด</t>
+          <t>มาริกี​     เบญจวิทยา</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>สตาร์แมนชั่น 74/17 ซ.ปรีดีพนมยงค์14 แยก8/1 ถ.สุขุมวิท71 แขวงพระโขนงเหนือ เขตวัฒนา กทม. 10110</t>
+          <t>51/9 ม.1 ต.หัวเขา​  อ.สิงหนคร​  จ.สงขลา</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>วัฒนา/ Vadhana</t>
+          <t>สิงหนคร/ Singhanakhon</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>สงขลา/ Songkhla</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>90280</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>660863684055</t>
+          <t>660816985629</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>P.</t>
+          <t>0816985629</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>155</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>23 Dec 2023 10:00</t>
+          <t>24 Dec 2023 12:10</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -1632,35 +1620,35 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>สตาร์แมนชั่น 74/17 ซ.ปรีดีพนมยงค์14 แยก8/1 ถ.สุขุมวิท71 แขวงพระโขนงเหนือ เขตวัฒนา กทม. 10110</t>
+          <t>51/9 ม.1 ต.หัวเขา​  อ.สิงหนคร​  จ.สงขลา</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>794639613998163</t>
+          <t>795083241528908</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>279</v>
+        <v>1860</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>279</v>
+        <v>1860</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -1687,67 +1675,63 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>จีรนันท์ เหรา</t>
+          <t>รัตติกร บัวจันทร์</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>193/9หมู่4 ซ.เอนกถาวร ต.พยอม อ.วังน้อย</t>
+          <t>44/25 ถ.คู่เมือง ต.ปากน้ำ อ.เมือง จ.กระบี่</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>วังน้อย/ Wang Noi</t>
+          <t>เมืองกระบี่/ Mueang Krabi</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>พระนครศรีอยุธยา/ Phra Nakhon Si Ayutthaya</t>
+          <t>กระบี่/ Krabi</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>13170</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0145564002872</t>
-        </is>
-      </c>
+          <t>81000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>660860794377</t>
+          <t>660806848860</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Jeeranunjj Hera</t>
+          <t>Rattikorn Buajan</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>279</v>
+        <v>1860</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>23 Dec 2023 10:06</t>
+          <t>24 Dec 2023 12:19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>193/9หมู่4 ซ.เอนกถาวร ต.พยอม อ.วังน้อย</t>
+          <t>44/25 ถ.คู่เมือง ต.ปากน้ำ อ.เมือง จ.กระบี่</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>794658875149222</t>
+          <t>795091610820504</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1795,39 +1779,39 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>สมเกียรติ จวบกลาง</t>
+          <t>จินดา ชวดชัยภูมิ หนิง</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>44ม.4ต.ด่านใน</t>
+          <t>21 ปานบุญอพาร์ทเม้นท์ ซ.พหลโยธิน 23 ถ.พหลโยธิน แขวงลาดยาว  ชั้น 2 ห้อง 207</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ด่านขุนทด/ Dan Khun Thot</t>
+          <t>จตุจักร/ Chatuchak</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>นครราชสีมา/ Nakhon Ratchasima</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>660958528318</t>
+          <t>660929267844</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0958528318</t>
+          <t>กรภัทร์ ชวดชัยภูมิ</t>
         </is>
       </c>
       <c r="Z13" t="n">
@@ -1835,44 +1819,44 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>23 Dec 2023 11:00</t>
+          <t>24 Dec 2023 12:25</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>44ม.4ต.ด่านใน</t>
+          <t>21 ปานบุญอพาร์ทเม้นท์ ซ.พหลโยธิน 23 ถ.พหลโยธิน แขวงลาดยาว  ชั้น 2 ห้อง 207</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>794685829510204</t>
+          <t>795093684760480</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ME6-000876</t>
+          <t>PR5-000627</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
+          <t>CANON PIXMA E4570 (PR5-000627) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>155</v>
+        <v>2590</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>465</v>
+        <v>2590</v>
       </c>
       <c r="H14" t="n">
         <v>-0</v>
@@ -1892,91 +1876,99 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>นางสงวน นุชเจริญ</t>
+          <t>จันทิรา บุญทันธ์</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>22/8 บ้านแห่เหนือ  · หนองบอน/ Nong Bon</t>
+          <t>709 ถนนพระรามที่ 2 แขวงบางมด</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>โกสุมพิสัย/ Kosum Phisai</t>
+          <t>จอมทอง/ Chom Thong</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>มหาสารคาม/ Maha Sarakham</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>44140</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr"/>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0105533122671</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>660836789590</t>
+          <t>660970066339</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0991463209</t>
+          <t>เบลสซิง นานาฮอนนี่</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>465</v>
+        <v>2590</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>23 Dec 2023 11:54</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>24 Dec 2023 12:56</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00001</t>
+        </is>
+      </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>22/8 บ้านแห่เหนือ  · หนองบอน/ Nong Bon</t>
+          <t>709 ถนนพระรามที่ 2 แขวงบางมด</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>794688247700158</t>
+          <t>795108827431088</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+          <t>MNL-001862</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+          <t>ACER LED Monitor EH200Qbi - 19.5"/TN/75Hz/3Y/MNL-001862</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>680</v>
+        <v>1890</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>2040</v>
+        <v>1890</v>
       </c>
       <c r="H15" t="n">
         <v>-0</v>
@@ -2003,95 +1995,95 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>กฤศมน แสงเดือน</t>
+          <t>วรเศรษฐ์ สนธยามาลย์</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>หจก.ร่ำรวยกรุ๊ป 365 เลขที่ 99/6 หมู่ที่ 3 บ้านห้วยเชียง ต.ลำภู</t>
+          <t>9/19-20 (โรงแรม เอส 33) ร้านโดโซะ</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>เมืองหนองบัวลำภู/ Nong Bua Lam Phu</t>
+          <t>คลองเตย/ Khlong Toei</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>หนองบัวลำภู/ Nongbua Lamphu</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0393565000683</t>
+          <t>0105560027455</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>660834928978</t>
+          <t>660953693825</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Naamny Cool-zaa</t>
+          <t>953693825</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>2040</v>
+        <v>1890</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>23 Dec 2023 12:09</t>
+          <t>24 Dec 2023 13:18</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>หจก.ร่ำรวยกรุ๊ป 365 เลขที่ 99/6 หมู่ที่ 3 บ้านห้วยเชียง ต.ลำภู</t>
+          <t>9/19-20 (โรงแรม เอส 33) ร้านโดโซะ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>794701637376289</t>
+          <t>795109840486946</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>CE1-005045</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
+          <t>SAMSUNG Galaxy A54 5G A546EZKDTHL  BLACK (8/256GB) (CE1-005045)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>120</v>
+        <v>14999</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>240</v>
+        <v>14999</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2111,95 +2103,91 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>อภิวัฒน์ วัฒนศิริบุตร</t>
+          <t>นาย  พัสกร  จะระ</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>โกดังลานรับซื้อพืชไร่ หมู่ 12 บ.เขารวก ต.หนองไผ่</t>
+          <t>บริษัท อมตะ บีกริม เพาเวอร์ ( ประตู 1 ) 700/370  ม.6   ต.หนองไม้แดง   อ.เมือง  จ.ชลบุรี  รหัสไปรษณีย์  20000 · หนองไม้แดง/ Nong Mai Daeng</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>หนองไผ่/ Nong Phai</t>
+          <t>เมืองชลบุรี/ Mueang Chon Buri</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>เพชรบูรณ์/ Phetchabun</t>
+          <t>ชลบุรี/ Chonburi</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>67140</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>660862166000</t>
+          <t>660924481675</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Misk Apiwat</t>
+          <t>0924481675</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>240</v>
+        <v>14999</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>23 Dec 2023 12:34</t>
+          <t>24 Dec 2023 13:24</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>โกดังลานรับซื้อพืชไร่ หมู่ 12 บ.เขารวก ต.หนองไผ่</t>
+          <t>บริษัท อมตะ บีกริม เพาเวอร์ ( ประตู 1 ) 700/370  ม.6   ต.หนองไม้แดง   อ.เมือง  จ.ชลบุรี  รหัสไปรษณีย์  20000 · หนองไม้แดง/ Nong Mai Daeng</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>794740058172800</t>
+          <t>795135894596019</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PR5-000503</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CANON PIXMA E-410 Black</t>
+          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1335</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>สี:ดำ</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1335</v>
+        <v>120</v>
       </c>
       <c r="H17" t="n">
         <v>-0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>Unpaid</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2219,84 +2207,84 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>วัชระ</t>
+          <t>ศิริพร​ อักษรพาลี</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>41/12 หมู่บ้านสายทิพย์วิลล่า หมู่3 ต.บางโทรัด · บางโทรัด/ Bang Tho Rat</t>
+          <t>บกจ.เสริมสงวนก่อสร้าง​ 139​หมู่2 · บ้านกลาง/ Ban Klang</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>เมืองสมุทรสาคร/ Mueang Samut Sakhon</t>
+          <t>อ่าวลึก/ Ao Luek</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>สมุทรสาคร/ Samut Sakhon</t>
+          <t>กระบี่/ Krabi</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>74000</t>
+          <t>81110</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>660644354322</t>
+          <t>660801484012</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Kinaree Rareong</t>
+          <t>*******012</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>1335</v>
+        <v>120</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>23 Dec 2023 14:16</t>
+          <t>24 Dec 2023 14:51</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>41/12 หมู่บ้านสายทิพย์วิลล่า หมู่3 ต.บางโทรัด · บางโทรัด/ Bang Tho Rat</t>
+          <t>บกจ.เสริมสงวนก่อสร้าง​ 139​หมู่2 · บ้านกลาง/ Ban Klang</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>794740400482619</t>
+          <t>795136862111045</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MS2-000960</t>
+          <t>SP2-001703</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen1 DataTraveler Exodia Onyx MS2-000960</t>
+          <t>BROTHER INK Cartridge BT-D60BK หมึกพิมพ์ SP2-001703</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -2323,47 +2311,47 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>ปฐม​ ชัยชนะ</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Passorn Pride Village, 207/79, Ton Pao, San Kamphaeng District, Chiang Mai 50130 · ต้นเปา/ Ton Pao</t>
+          <t>โรงเรียนอนุบาลเพลงพิณ​ 95/40​ ม.6​ ต.มะเร็ต​</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>สันกำแพง/ San Kamphaeng</t>
+          <t>เกาะสมุย/ Ko Samui</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>สุราษฎร์ธานี/ Surat Thani</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>50130</t>
+          <t>84310</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>660855411599</t>
+          <t>660966535593</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Shein</t>
+          <t>ปฐม ชัยชนะ</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>23 Dec 2023 13:52</t>
+          <t>24 Dec 2023 14:43</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr"/>
@@ -2372,35 +2360,35 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>Passorn Pride Village, 207/79, Ton Pao, San Kamphaeng District, Chiang Mai 50130 · ต้นเปา/ Ton Pao</t>
+          <t>โรงเรียนอนุบาลเพลงพิณ​ 95/40​ ม.6​ ต.มะเร็ต​</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>794813284487985</t>
+          <t>795168489704309</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MS4-000931</t>
+          <t>ME6-000876</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SANDISK Extreme SDSSDE61 Portable SSD 1TB (Sky-Blue color) MS4-000931</t>
+          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2990</v>
+        <v>155</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>2990</v>
+        <v>155</v>
       </c>
       <c r="H19" t="n">
         <v>-0</v>
@@ -2427,88 +2415,84 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>ญาณา เลาสุขศรี</t>
+          <t>นาย สอาด อินท์นัอย</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>103/51 ซอยลาดพร้าว 26 ถนนลาดพร้าว แขวงจอมพล เขตจตุจักร</t>
+          <t>54/4 ม.2 ต.หาดทรายรี อ.เมือง จ.ชุมพร 86120</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>จตุจักร/ Chatuchak</t>
+          <t>เมืองชุมพร/ Mueang Chumphon</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>ชุมพร/ Chumphon</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>10900</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>1101401257647</t>
-        </is>
-      </c>
+          <t>86120</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>660824965461</t>
+          <t>660946404392</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Yana Laosooksri</t>
+          <t>0801096035</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>2990</v>
+        <v>155</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>23 Dec 2023 18:10</t>
+          <t>24 Dec 2023 16:14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>103/51 ซอยลาดพร้าว 26 ถนนลาดพร้าว แขวงจอมพล เขตจตุจักร</t>
+          <t>54/4 ม.2 ต.หาดทรายรี อ.เมือง จ.ชุมพร 86120</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>794848263259988</t>
+          <t>795193009416184</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PR6-000405</t>
+          <t>MNL-001916</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HP Laser MFP 135w / 4ZB83A (3Y*) (PR6-000405) พร้อมโทนเนอร์แท้ในกล่อง 1 ชุด</t>
+          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4590</v>
+        <v>6990</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>4590</v>
+        <v>6990</v>
       </c>
       <c r="H20" t="n">
         <v>-0</v>
@@ -2535,47 +2519,47 @@
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>SIRAVICH SOPONWATTANA</t>
+          <t>รชานนท์  โชติบุตร</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>271 ม.7 ซ.เทศบาลบางปู2/1 ถ.ท้ายบ้าน ต.ท้ายบ้าน อ.เมือง</t>
+          <t>joy บ้านเลขที่99/24 หมู่ 2, ซอยวัดลำโพ, ต.ลำโพ</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>เมืองสมุทรปราการ/ Mueang Samut Prakan</t>
+          <t>บางบัวทอง/ Bang Bua Thong</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>สมุทรปราการ/ Samut Prakan</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>660868082555</t>
+          <t>660819250822</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Siravich Soponwattana</t>
+          <t>0819250822</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>4590</v>
+        <v>6990</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>23 Dec 2023 19:53</t>
+          <t>24 Dec 2023 17:07</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
@@ -2584,35 +2568,35 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>271 ม.7 ซ.เทศบาลบางปู2/1 ถ.ท้ายบ้าน ต.ท้ายบ้าน อ.เมือง</t>
+          <t>joy บ้านเลขที่99/24 หมู่ 2, ซอยวัดลำโพ, ต.ลำโพ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>794864056743850</t>
+          <t>795193882369576</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MS2-000944</t>
+          <t>PR5-000612</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
+          <t>Epson EcoTank L4260 A4 Wi-Fi Duplex All-in-One Ink Tank Printer (Print/Copy/Scan/WiFi-Direct)(PR5-000612) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>135</v>
+        <v>6890</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>135</v>
+        <v>6890</v>
       </c>
       <c r="H21" t="n">
         <v>-0</v>
@@ -2639,84 +2623,84 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>สมพร จันทร์หอม</t>
+          <t>สะฝีย้ะ สำลี</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>95 ม.5 ต.สวนป่าน  · สวนป่าน/ Suan Pan</t>
+          <t>22/1หมู่4 ต คุระ อ คุระบุรี จ พังงา</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>เมืองนครปฐม/ Mueang Nakhon Pathom</t>
+          <t>คุระบุรี/ Khura Buri</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>นครปฐม/ Nakhon Pathom</t>
+          <t>พังงา/ Phang Nga</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>73000</t>
+          <t>82150</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>660984930601</t>
+          <t>660936749745</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>อินทิรา จันทร์หอม</t>
+          <t>ซาฟีย๊ะห์ สำลี</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>135</v>
+        <v>6890</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>23 Dec 2023 20:32</t>
+          <t>24 Dec 2023 17:46</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>95 ม.5 ต.สวนป่าน  · สวนป่าน/ Suan Pan</t>
+          <t>22/1หมู่4 ต คุระ อ คุระบุรี จ พังงา</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>794867450276020</t>
+          <t>795205459559120</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MS2-000944</t>
+          <t>WIH-000001</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
+          <t>WISE หูฟังมีสาย Type-C Stereo Earphones (HS-500) (WIH-000001)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>135</v>
+        <v>299</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>135</v>
+        <v>299</v>
       </c>
       <c r="H22" t="n">
         <v>-0</v>
@@ -2743,47 +2727,47 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>ภูวดล พุ่มพวง</t>
+          <t>ชชาติ จันทร์ทอง</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>7/152 หมู่บ้านอมรพันธ์ ซอยเทิดราชัน13 ถนนเทิดราชัน แขวงสีกัน</t>
+          <t>345 อาคารซีพีทาวเวอร์ ถนนพัฒนาการคูขวาง ตำบลในเมือง · ในเมือง/ Nai Mueang</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>ดอนเมือง/ Don Mueang</t>
+          <t>เมืองนครศรีธรรมราช/ Mueang Nakhon Si Thammarat</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>นครศรีธรรมราช/ Nakhon Si Thammarat</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>660616029688</t>
+          <t>660879060002</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>phuvadol</t>
+          <t>ชชาติ จันทร์ทอง</t>
         </is>
       </c>
       <c r="Z22" t="n">
-        <v>135</v>
+        <v>299</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>23 Dec 2023 20:35</t>
+          <t>24 Dec 2023 18:08</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
@@ -2792,35 +2776,35 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7/152 หมู่บ้านอมรพันธ์ ซอยเทิดราชัน13 ถนนเทิดราชัน แขวงสีกัน</t>
+          <t>345 อาคารซีพีทาวเวอร์ ถนนพัฒนาการคูขวาง ตำบลในเมือง · ในเมือง/ Nai Mueang</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>794872044474928</t>
+          <t>795242894233004</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1860</v>
+        <v>120</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>1860</v>
+        <v>600</v>
       </c>
       <c r="H23" t="n">
         <v>-0</v>
@@ -2847,84 +2831,88 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>ยลดา</t>
+          <t>มัลลิกา แก้วพาณิชย์</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>- 416/1 สายันต์อพาร์ตเมนต์ตึกบี ต.ป่าไร่</t>
+          <t>โรงสีย่งเส็ง 5 (บ้านชี) 142 ม.1</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>อรัญประเทศ/ Aranyaprathet</t>
+          <t>บ้านหมี่/ Ban Mi</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>สระแก้ว/ Sa Kaeo</t>
+          <t>ลพบุรี/ Lopburi</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>660618769264</t>
+          <t>660899958533</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>zibblyy</t>
+          <t>มัลลิกา แก้วพาณิชย์</t>
         </is>
       </c>
       <c r="Z23" t="n">
-        <v>1860</v>
+        <v>600</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>23 Dec 2023 20:47</t>
+          <t>24 Dec 2023 20:07</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>- 416/1 สายันต์อพาร์ตเมนต์ตึกบี ต.ป่าไร่</t>
+          <t>โรงสีย่งเส็ง 5 (บ้านชี) 142 ม.1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>794876219686228</t>
+          <t>795306823750355</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MNL-001799</t>
+          <t>SP2-001617</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SAMSUNG Odyssey G5 Gaming Monitor 27" LS27CG510EEXXT VA/165Hz/1ms/2K QHD MNL-001799</t>
+          <t>HP GT52 Ink Bottle Y MOH56AA SP2-001617</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7490</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>245</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>สี:สีเหลือง</t>
+        </is>
+      </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>7490</v>
+        <v>245</v>
       </c>
       <c r="H24" t="n">
         <v>-0</v>
@@ -2951,84 +2939,84 @@
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>คำรณ สีธรรมมา</t>
+          <t>ปริยกร ศรีลา</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>บ้านเลขที่25หมู่ 2 ตำบลหนองตะไก้ อำเภอสูงเนินจังหวัดนครราชสีมา 30380 · หนองตะไก้/ Nong Takai</t>
+          <t>358-360 หมู่ 5 ถนนซุปเปอร์ไฮเวย์ เชียงใหม่-ลำปาง ตำบลป่าตั</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>สูงเนิน/ Sung Noen</t>
+          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>นครราชสีมา/ Nakhon Ratchasima</t>
+          <t>เชียงใหม่/ Chiang Mai</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
-          <t>660615141998</t>
+          <t>660806711807</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>M4A1</t>
+          <t>Khongfang Pariya</t>
         </is>
       </c>
       <c r="Z24" t="n">
-        <v>7490</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>23 Dec 2023 20:44</t>
+          <t>24 Dec 2023 22:40</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>บ้านเลขที่25หมู่ 2 ตำบลหนองตะไก้ อำเภอสูงเนินจังหวัดนครราชสีมา 30380 · หนองตะไก้/ Nong Takai</t>
+          <t>358-360 หมู่ 5 ถนนซุปเปอร์ไฮเวย์ เชียงใหม่-ลำปาง ตำบลป่าตั</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>794879850049169</t>
+          <t>795326253442287</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MS2-000944</t>
+          <t>SP2-001778</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
+          <t>HP 682 Black Original Ink Cartridge / 3YM77AA SP2-001778</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>135</v>
+        <v>390</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="H25" t="n">
         <v>-0</v>
@@ -3055,51 +3043,47 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>บริษัท​ แอฟ​ฟิกซ์​ เทคโนโลยี​ จำกัด</t>
+          <t>ทิพรัตน์ ลิ่มปิติมงคล</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>32/144 ถ.สุขุมวิท​ ต.ปากน้ำ</t>
+          <t>5/89 ซอยรองเมือง 5 แขวงรองเมือง เขตปทุมวัน</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>เมืองสมุทรปราการ/ Mueang Samut Prakan</t>
+          <t>ปทุมวัน/ Pathum Wan</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>สมุทรปราการ/ Samut Prakan</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>10270</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>0115555001222</t>
-        </is>
-      </c>
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
-          <t>660824940909</t>
+          <t>660948969442</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>วิสุทธิ์​</t>
+          <t>ทิพรัตน์ ลิ่มปิติมงคล</t>
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>23 Dec 2023 21:00</t>
+          <t>25 Dec 2023 00:09</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -3108,35 +3092,35 @@
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>32/144 ถ.สุขุมวิท​ ต.ปากน้ำ</t>
+          <t>5/89 ซอยรองเมือง 5 แขวงรองเมือง เขตปทุมวัน</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>794907415644229</t>
+          <t>795335652667715</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MNL-001849</t>
+          <t>ME6-000875</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAMSUNG Smart LED Monitor M7 32"LS32CM701UEXXT VA/60Hz/4ms/4K MNL-001849</t>
+          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13900</v>
+        <v>109</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>13900</v>
+        <v>327</v>
       </c>
       <c r="H26" t="n">
         <v>-0</v>
@@ -3163,84 +3147,88 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Ning Thanukanokmard</t>
+          <t>อภิลักษณ์ ธนากรพูนผล</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>19 Moo.3 · มีชัย/ Mi Chai</t>
+          <t>373/95 ซอย17 ม.ทิพมาศเสรีบางนา ต.บางบ่</t>
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>เมืองหนองคาย/ Mueang Nong Khai</t>
+          <t>บางบ่อ/ Bang Bo</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>หนองคาย/ Nong Khai</t>
+          <t>สมุทรปราการ/ Samut Prakan</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>43000</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>10560</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>1640600095943</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>660823115996</t>
+          <t>660864645969</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Hyeunjae Kim</t>
+          <t>Apilux Thanakornphoonphol</t>
         </is>
       </c>
       <c r="Z26" t="n">
-        <v>13900</v>
+        <v>327</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>23 Dec 2023 22:15</t>
+          <t>25 Dec 2023 00:29</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
-        <v>87.5</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>19 Moo.3 · มีชัย/ Mi Chai</t>
+          <t>373/95 ซอย17 ม.ทิพมาศเสรีบางนา ต.บางบ่</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>794925677461973</t>
+          <t>795359049859182</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ME6-000875</t>
+          <t>AC7-000890</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
+          <t>PHILIPS ปลั๊กไฟ 4ช่อง 4สวิสต์ 3M (2Y) AC7-000890</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>109</v>
+        <v>379</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>368</v>
+        <v>898</v>
       </c>
       <c r="H27" t="n">
         <v>-0</v>
@@ -3267,84 +3255,88 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>กานต์ธิดา ภูชมศรี</t>
+          <t>อภิชัย บุพพัณหสมัย</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>22/3 ม.2 ต.หนองกร่าง อ.บ่อพลอย</t>
+          <t>บริษัท ซีเทค ออโต้ พาร์ท จำกัด 92 หมู่ที่2 ถนนพหลโยธิน ตำบลลำไทร · ลำไทร/ Lam Sai</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>บ่อพลอย/ Bo Phloi</t>
+          <t>วังน้อย/ Wang Noi</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>กาญจนบุรี/ Kanchanaburi</t>
+          <t>พระนครศรีอยุธยา/ Phra Nakhon Si Ayutthaya</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>71220</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+          <t>13170</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>0145555000722</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>660984470724</t>
+          <t>660645656392</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Kantida Phuchomsri</t>
+          <t>*******645</t>
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>368</v>
+        <v>898</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>23 Dec 2023 23:58</t>
+          <t>25 Dec 2023 03:04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>22/3 ม.2 ต.หนองกร่าง อ.บ่อพลอย</t>
+          <t>บริษัท ซีเทค ออโต้ พาร์ท จำกัด 92 หมู่ที่2 ถนนพหลโยธิน ตำบลลำไทร · ลำไทร/ Lam Sai</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>794925677461973</t>
+          <t>795359049859182</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MS2-000754</t>
+          <t>AC7-000893</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANDISK USB2.0 Cruzer Blade 64GB MS2-000754</t>
+          <t>PHILIPS ปลั๊กไฟ 5ช่อง 5สวิสต์ 5M (2Y) AC7-000893</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>150</v>
+        <v>519</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>368</v>
+        <v>898</v>
       </c>
       <c r="H28" t="n">
         <v>-0</v>
@@ -3371,84 +3363,88 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>กานต์ธิดา ภูชมศรี</t>
+          <t>อภิชัย บุพพัณหสมัย</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>22/3 ม.2 ต.หนองกร่าง อ.บ่อพลอย</t>
+          <t>บริษัท ซีเทค ออโต้ พาร์ท จำกัด 92 หมู่ที่2 ถนนพหลโยธิน ตำบลลำไทร · ลำไทร/ Lam Sai</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>บ่อพลอย/ Bo Phloi</t>
+          <t>วังน้อย/ Wang Noi</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>กาญจนบุรี/ Kanchanaburi</t>
+          <t>พระนครศรีอยุธยา/ Phra Nakhon Si Ayutthaya</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>71220</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr"/>
+          <t>13170</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>0145555000722</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>660984470724</t>
+          <t>660645656392</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Kantida Phuchomsri</t>
+          <t>*******645</t>
         </is>
       </c>
       <c r="Z28" t="n">
-        <v>368</v>
+        <v>898</v>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>23 Dec 2023 23:58</t>
+          <t>25 Dec 2023 03:04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>22/3 ม.2 ต.หนองกร่าง อ.บ่อพลอย</t>
+          <t>บริษัท ซีเทค ออโต้ พาร์ท จำกัด 92 หมู่ที่2 ถนนพหลโยธิน ตำบลลำไทร · ลำไทร/ Lam Sai</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>794934231327542</t>
+          <t>795383614952098</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ME6-000970</t>
+          <t>MS2-000960</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
+          <t>KINGSTON 64GB USB3.2 Gen1 DataTraveler Exodia Onyx MS2-000960</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="H29" t="n">
         <v>-0</v>
@@ -3475,12 +3471,12 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>บริษัท เอเชี่ยนแอร์โรสเปซเซอร์วิส จำกัด</t>
+          <t>พล</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>65/198 อาคารชำนาญเพ็ญชาติบิสเนสเซ็นเตอร์ ชั้นที่ 23 ถนนพระราม 9 แขวงห้วยขวาง</t>
+          <t>เลขที่ 317 ถนนประชาราษฎร์เขตห้วยขวาง หน้าซอย8กรุงเทพมหานคร บริษัท ซันชายไบโอเทด อินเตอร์เนชั่นแนล จำกัด · ห้วยขวาง/ Huai Khwang</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3499,71 +3495,67 @@
           <t>10310</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>0105546033311</t>
-        </is>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>66026430740</t>
+          <t>660933730454</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>บุญชัย พจนาสมสมาน</t>
+          <t>0933730454</t>
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>299</v>
+        <v>135</v>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>24 Dec 2023 00:10</t>
+          <t>25 Dec 2023 06:17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>65/198 อาคารชำนาญเพ็ญชาติบิสเนสเซ็นเตอร์ ชั้นที่ 23 ถนนพระราม 9 แขวงห้วยขวาง</t>
+          <t>เลขที่ 317 ถนนประชาราษฎร์เขตห้วยขวาง หน้าซอย8กรุงเทพมหานคร บริษัท ซันชายไบโอเทด อินเตอร์เนชั่นแนล จำกัด · ห้วยขวาง/ Huai Khwang</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>794945821778234</t>
+          <t>795392662352155</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MS4-000939</t>
+          <t>MS2-000960</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SANDISK SDSSDE30 Portable SSD 1TB (Read speed up to 800MB/s,) MS4-000939</t>
+          <t>KINGSTON 64GB USB3.2 Gen1 DataTraveler Exodia Onyx MS2-000960</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2290</v>
+        <v>135</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>2290</v>
+        <v>135</v>
       </c>
       <c r="H30" t="n">
         <v>-0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3583,47 +3575,47 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>พตท. กฤษฏิ์พันธุ์ ล่ำภากร</t>
+          <t>พนิดา กาเซ็ง</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>หมู่บ้านเดอะคลัสเตอร์วิลล์ 2 เลขที่ 109/60 ซอย 4 บางขุนกอง</t>
+          <t>ตำบลธารน้ำทิพย์ 50/4</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>บางกรวย/ Bang Kruai</t>
+          <t>เบตง/ Betong</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>ยะลา/ Yala</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>95110</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>660874854442</t>
+          <t>660889575809</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Gritphan Lumpakorn</t>
+          <t>Anas Lateh</t>
         </is>
       </c>
       <c r="Z30" t="n">
-        <v>2290</v>
+        <v>135</v>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>24 Dec 2023 00:59</t>
+          <t>25 Dec 2023 07:18</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -3632,42 +3624,42 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>หมู่บ้านเดอะคลัสเตอร์วิลล์ 2 เลขที่ 109/60 ซอย 4 บางขุนกอง</t>
+          <t>ตำบลธารน้ำทิพย์ 50/4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>794960498511360</t>
+          <t>795423096245869</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MS2-000917</t>
+          <t>ME6-000901</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KINGSTON Kyson DTKN USB A 32GB/5Y MS2-000917</t>
+          <t>SANDISK Micro SD Ultra 32GB, 100MB/s read, C10 ME6-000901</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="H31" t="n">
         <v>-0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -3687,84 +3679,84 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Mikhail Khalizev</t>
+          <t>ประมวณ วรรณโชติ</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Allamanda 3 Condominium, Ground floor Unit 3130 · เชิงทะเล/ Choeng Thale</t>
+          <t>247/29 ถ.มหิดล ต.ช้างคลาน</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>ถลาง/ Thalang</t>
+          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>ภูเก็ต/ Phuket</t>
+          <t>เชียงใหม่/ Chiang Mai</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>83110</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>660629478177</t>
+          <t>660817647936</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Mikhail Khalizev</t>
+          <t>ตถตา</t>
         </is>
       </c>
       <c r="Z31" t="n">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>24 Dec 2023 05:48</t>
+          <t>25 Dec 2023 09:13</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Allamanda 3 Condominium, Ground floor Unit 3130 · เชิงทะเล/ Choeng Thale</t>
+          <t>247/29 ถ.มหิดล ต.ช้างคลาน</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>794964650322439</t>
+          <t>799858548970134</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>ME6-000914</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>KINGSTON SD Canvas GO Plus 64GB 170/70MB/s ME6-000914</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1860</v>
+        <v>229</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1860</v>
+        <v>229</v>
       </c>
       <c r="H32" t="n">
         <v>-0</v>
@@ -3791,84 +3783,84 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>กฤติพงษ์ รักพานิชมณี</t>
+          <t>นายธนภัทร ผิวเงิน</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>111/37 หมู่ที่ 14 ปันนา3เรสชิเดนท์ ห้อง419 ซ.7 ถ.สุเทพ ต.สุเทพ</t>
+          <t>ร้านถ่ายรูปบ้านขาม 260 หมู่ 10 บ้านนาขาม ตำบลศรีชมภู</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
+          <t>โซ่พิสัย/ So Phisai</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>บึงกาฬ/ Bueng Kan</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>38170</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>660869322999</t>
+          <t>660957038298</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>กฤติพงษ์ รักพานิชมณี</t>
+          <t>นายธนภัทร ผิวเงิน</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>1860</v>
+        <v>229</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>24 Dec 2023 05:32</t>
+          <t>25 Dec 2023 07:51</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>111/37 หมู่ที่ 14 ปันนา3เรสชิเดนท์ ห้อง419 ซ.7 ถ.สุเทพ ต.สุเทพ</t>
+          <t>ร้านถ่ายรูปบ้านขาม 260 หมู่ 10 บ้านนาขาม ตำบลศรีชมภู</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>794967084728279</t>
+          <t>799929924712449</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CU2-000471</t>
+          <t>SP2-1713+SP2-1714+SP2-1715+SP2-1716</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMD RYZEN 5 4600G 3.7GHz (6Cores/12Threads) AM4 (3Y) CU2-000471</t>
+          <t>Epson หมึกแท้รุ่น T00V (003) Ink Bottle Set 4 สี (SP2-1713+SP2-1714+SP2-1715+SP2-1716)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3690</v>
+        <v>800</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>3690</v>
+        <v>800</v>
       </c>
       <c r="H33" t="n">
         <v>-0</v>
@@ -3895,18 +3887,18 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>วินัย พรมบุญ</t>
+          <t>Zaw Min Tun</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>26/12 คอนโดเทเวศน์ ชั้น 1 ซ.นามบัญญัติ แขวงบางขุ่นพรหม</t>
+          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>พระนคร/ Phra Nakhon</t>
+          <t>คลองเตย/ Khlong Toei</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3916,63 +3908,63 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
-          <t>660647876435</t>
+          <t>660829623134</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Mahiro LW</t>
+          <t>JH Aung Aung</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>3690</v>
+        <v>800</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>24 Dec 2023 06:29</t>
+          <t>24 Dec 2023 01:32</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>26/12 คอนโดเทเวศน์ ชั้น 1 ซ.นามบัญญัติ แขวงบางขุ่นพรหม</t>
+          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>795000400748860</t>
+          <t>799930194244423</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ME6-000877</t>
+          <t>ME6-000876</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 128GB, 100/85MB/s ME6-000877</t>
+          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="H34" t="n">
         <v>-0</v>
@@ -3999,47 +3991,47 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Jariyaporn Breuel</t>
+          <t>ภูษิต  ปาปะเก</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>252 mu 12 Ban Thung Seng Thong Tambon Waeng</t>
+          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>โพนทอง/ Phon Thong</t>
+          <t>เมืองสมุทรปราการ/ Mueang Samut Prakan</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>ร้อยเอ็ด/ Roi Et</t>
+          <t>สมุทรปราการ/ Samut Prakan</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
-          <t>660929814561</t>
+          <t>660890528126</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Jariyaporn Breuel</t>
+          <t>ภูษิต  ปาปะเก</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>24 Dec 2023 08:33</t>
+          <t>24 Dec 2023 03:33</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
@@ -4048,42 +4040,42 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>252 mu 12 Ban Thung Seng Thong Tambon Waeng</t>
+          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>795001246312124</t>
+          <t>799963152618334</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ME6-000916</t>
+          <t>ME6-000960</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSD Canvas GO Plus 64GB 170/70MB/s ME6-000916</t>
+          <t>SanDisk Ultra microSDXC, SQUAB 64GB, A1, C10, U1, UHS-I, 140MB/s R, 4x6, 10Y</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>245</v>
+        <v>195</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>490</v>
+        <v>195</v>
       </c>
       <c r="H35" t="n">
         <v>-0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -4103,91 +4095,95 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Oliver Bohmlander</t>
+          <t>อังษณา พรมทัณ</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>55/3 Village No. 5 Klong Rang Na mom · นาหม่อม/ Na Mom</t>
+          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>นาหม่อม/ Na Mom</t>
+          <t>ดุสิต/ Dusit</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>สงขลา/ Songkhla</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>90310</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr"/>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>1103700155899</t>
+        </is>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>660618643392</t>
+          <t>660898881040</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>618643392</t>
+          <t>อังษณา พรมทัณ</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>490</v>
+        <v>195</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>24 Dec 2023 08:53</t>
+          <t>24 Dec 2023 07:45</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>55/3 Village No. 5 Klong Rang Na mom · นาหม่อม/ Na Mom</t>
+          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>795040470960074</t>
+          <t>799969900750744</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>MS2-000944</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1860</v>
+        <v>135</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1860</v>
+        <v>135</v>
       </c>
       <c r="H36" t="n">
         <v>-0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -4207,91 +4203,91 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>ว่าที่ร้อยตรีทิวากร ทุมมา</t>
+          <t>รพีพงศ์ ศศิธรวัณณ์</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>23 หมู่ที่ 4 · นาบินหลา/ Na Bin La</t>
+          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>เมืองตรัง/ Mueang Trang</t>
+          <t>เมืองนนทบุรี/ Mueang Nonthaburi</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>ตรัง/ Trang</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>92170</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
-          <t>660610699016</t>
+          <t>660982523524</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>0970132826</t>
+          <t>Reaw</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>1860</v>
+        <v>135</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>24 Dec 2023 10:54</t>
+          <t>24 Dec 2023 07:46</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>80.67</v>
+        <v>29</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>23 หมู่ที่ 4 · นาบินหลา/ Na Bin La</t>
+          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>795057611462381</t>
+          <t>799979507148952</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IP4-002000</t>
+          <t>IP7-001199</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LOGITECH SIGNATURE M650 WIRELESS MOUSE ROSE (1Y) IP4-002000</t>
+          <t>LOGITECH COMBO TOUCH FOR iPAD 10th GENERATION (1Y) IP7-001199 (จำนวนจำกัด)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>869</v>
+        <v>3790</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>869</v>
+        <v>3790</v>
       </c>
       <c r="H37" t="n">
         <v>-0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -4311,91 +4307,91 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>ศิริเดือน พลับประสิทธิ์</t>
+          <t>HADIN</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>171/110 มบ. ทัศนีย์ ซ.6 ซ. พุทธบูชา 39แยก1-1 ถ. พุทธบูชา แขวงบางมด</t>
+          <t>198/4, Moo 10</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>ทุ่งครุ/ Thung Khru</t>
+          <t>หางดง/ Hang Dong</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>เชียงใหม่/ Chiang Mai</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
-          <t>660863642948</t>
+          <t>660828210693</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>ศิริเดือน พลับประสิทธิ์</t>
+          <t>Mehdi Hadim</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>869</v>
+        <v>3790</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>24 Dec 2023 11:05</t>
+          <t>24 Dec 2023 08:21</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>171/110 มบ. ทัศนีย์ ซ.6 ซ. พุทธบูชา 39แยก1-1 ถ. พุทธบูชา แขวงบางมด</t>
+          <t>198/4, Moo 10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>795079830574423</t>
+          <t>800009590366429</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ME6-000876</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
+          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="H38" t="n">
         <v>-0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -4415,91 +4411,95 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>มาริกี​     เบญจวิทยา</t>
+          <t>มลฤดี  รู้รักตน</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>51/9 ม.1 ต.หัวเขา​  อ.สิงหนคร​  จ.สงขลา</t>
+          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>สิงหนคร/ Singhanakhon</t>
+          <t>ปากเกร็ด/ Pak Kret</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>สงขลา/ Songkhla</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>90280</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>0125537003979</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>660816985629</t>
+          <t>660899910145</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0816985629</t>
+          <t>Monludee Rurakton</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>24 Dec 2023 12:10</t>
+          <t>24 Dec 2023 10:12</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>51/9 ม.1 ต.หัวเขา​  อ.สิงหนคร​  จ.สงขลา</t>
+          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>795083241528908</t>
+          <t>800045958990703</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>MNL-001862</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>ACER LED Monitor EH200Qbi - 19.5"/TN/75Hz/3Y/MNL-001862</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1860</v>
+        <v>1890</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1860</v>
+        <v>1890</v>
       </c>
       <c r="H39" t="n">
         <v>-0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -4519,91 +4519,91 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>รัตติกร บัวจันทร์</t>
+          <t>นายคณกฤช มัชฌิมา</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>44/25 ถ.คู่เมือง ต.ปากน้ำ อ.เมือง จ.กระบี่</t>
+          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>เมืองกระบี่/ Mueang Krabi</t>
+          <t>เมืองพิจิตร/ Mueang Phichit</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>กระบี่/ Krabi</t>
+          <t>พิจิตร/ Phichit</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>81000</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
-          <t>660806848860</t>
+          <t>66899594344</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Rattikorn Buajan</t>
+          <t>นายคณกฤช  มัชฌิมา</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>1860</v>
+        <v>1890</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>24 Dec 2023 12:19</t>
+          <t>24 Dec 2023 11:35</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>44/25 ถ.คู่เมือง ต.ปากน้ำ อ.เมือง จ.กระบี่</t>
+          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>795091610820504</t>
+          <t>800074729069035</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>PR5-000610</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>EPSON Printer L3210 STD/C11CJ68501 (PR5-000610) (จำกัดการซื้อ1ออเดอร์ไม่เกิน3เครื่อง) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1860</v>
+        <v>3730</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1860</v>
+        <v>3730</v>
       </c>
       <c r="H40" t="n">
         <v>-0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -4623,91 +4623,95 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>จินดา ชวดชัยภูมิ หนิง</t>
+          <t>เฉลิม พรพงษ์</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>21 ปานบุญอพาร์ทเม้นท์ ซ.พหลโยธิน 23 ถ.พหลโยธิน แขวงลาดยาว  ชั้น 2 ห้อง 207</t>
+          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>จตุจักร/ Chatuchak</t>
+          <t>ธัญบุรี/ Thanyaburi</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>ปทุมธานี/ Pathum Thani</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>10900</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr"/>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>1195703950</t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>660929267844</t>
+          <t>660838464600</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>กรภัทร์ ชวดชัยภูมิ</t>
+          <t>Chaloem Phornphong</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>1860</v>
+        <v>3730</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>24 Dec 2023 12:25</t>
+          <t>24 Dec 2023 12:43</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>21 ปานบุญอพาร์ทเม้นท์ ซ.พหลโยธิน 23 ถ.พหลโยธิน แขวงลาดยาว  ชั้น 2 ห้อง 207</t>
+          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>795093684760480</t>
+          <t>800085587433269</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PR5-000627</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CANON PIXMA E4570 (PR5-000627) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2590</v>
+        <v>1860</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
         <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>2590</v>
+        <v>1860</v>
       </c>
       <c r="H41" t="n">
         <v>-0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -4720,106 +4724,98 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>สาขาย่อย</t>
+          <t>สำนักงานใหญ่</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>จันทิรา บุญทันธ์</t>
+          <t>สมภพ บูรณพิมพ์</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>709 ถนนพระรามที่ 2 แขวงบางมด</t>
+          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>จอมทอง/ Chom Thong</t>
+          <t>บ้านบึง/ Ban Bueng</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>ชลบุรี/ Chonburi</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>10150</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>0105533122671</t>
-        </is>
-      </c>
+          <t>20220</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
-          <t>660970066339</t>
+          <t>660894014557</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>เบลสซิง นานาฮอนนี่</t>
+          <t>*******874</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>2590</v>
+        <v>1860</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>24 Dec 2023 12:56</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
+          <t>24 Dec 2023 13:30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>709 ถนนพระรามที่ 2 แขวงบางมด</t>
+          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>795108827431088</t>
+          <t>800090726148364</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MNL-001862</t>
+          <t>MS2-000844</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ACER LED Monitor EH200Qbi - 19.5"/TN/75Hz/3Y/MNL-001862</t>
+          <t>SANDISK USB2.0 Cruzer Blade 16GB MS2-000844</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1890</v>
+        <v>115</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1890</v>
+        <v>115</v>
       </c>
       <c r="H42" t="n">
         <v>-0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -4839,95 +4835,95 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>วรเศรษฐ์ สนธยามาลย์</t>
+          <t>นาย จิรวัฒน์ อ่อนคล้าย</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>9/19-20 (โรงแรม เอส 33) ร้านโดโซะ</t>
+          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>คลองเตย/ Khlong Toei</t>
+          <t>ตาคลี/ Takhli</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>นครสวรรค์/ Nakhon Sawan</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>10110</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>0105560027455</t>
-        </is>
-      </c>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
-          <t>660953693825</t>
+          <t>660814081091</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>953693825</t>
+          <t>0814081091</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>1890</v>
+        <v>115</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>24 Dec 2023 13:18</t>
+          <t>24 Dec 2023 13:23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>9/19-20 (โรงแรม เอส 33) ร้านโดโซะ</t>
+          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>795109840486946</t>
+          <t>800094782668343</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CE1-005045</t>
+          <t>PR5-000503</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SAMSUNG Galaxy A54 5G A546EZKDTHL  BLACK (8/256GB) (CE1-005045)</t>
+          <t>CANON PIXMA E-410 Black</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14999</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1335</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Color Family:Black</t>
+        </is>
+      </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>14999</v>
+        <v>1335</v>
       </c>
       <c r="H43" t="n">
         <v>-0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -4947,91 +4943,91 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>นาย  พัสกร  จะระ</t>
+          <t>Ethel Joy</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>บริษัท อมตะ บีกริม เพาเวอร์ ( ประตู 1 ) 700/370  ม.6   ต.หนองไม้แดง   อ.เมือง  จ.ชลบุรี  รหัสไปรษณีย์  20000 · หนองไม้แดง/ Nong Mai Daeng</t>
+          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>เมืองชลบุรี/ Mueang Chon Buri</t>
+          <t>บางบัวทอง/ Bang Bua Thong</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>ชลบุรี/ Chonburi</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>660924481675</t>
+          <t>660832393046</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>0924481675</t>
+          <t>Ethel Joy</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>14999</v>
+        <v>1335</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>24 Dec 2023 13:24</t>
+          <t>24 Dec 2023 13:51</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>บริษัท อมตะ บีกริม เพาเวอร์ ( ประตู 1 ) 700/370  ม.6   ต.หนองไม้แดง   อ.เมือง  จ.ชลบุรี  รหัสไปรษณีย์  20000 · หนองไม้แดง/ Nong Mai Daeng</t>
+          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>795135894596019</t>
+          <t>800122510696050</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001753</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>120</v>
+        <v>279</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>120</v>
+        <v>279</v>
       </c>
       <c r="H44" t="n">
         <v>-0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -5051,91 +5047,91 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ศิริพร​ อักษรพาลี</t>
+          <t>ศิริกัญญา​ โต​เจริญ​</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>บกจ.เสริมสงวนก่อสร้าง​ 139​หมู่2 · บ้านกลาง/ Ban Klang</t>
+          <t>12ม.6ต.บางแก้ว</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>อ่าวลึก/ Ao Luek</t>
+          <t>เมืองฉะเชิงเทรา/ Mueang Chachoengsao</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>กระบี่/ Krabi</t>
+          <t>ฉะเชิงเทรา/ Chachoengsao</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>81110</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>660801484012</t>
+          <t>660819831278</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>*******012</t>
+          <t>ศิริกัญญา โตเจริญ</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>120</v>
+        <v>279</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>24 Dec 2023 14:51</t>
+          <t>24 Dec 2023 14:40</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>บกจ.เสริมสงวนก่อสร้าง​ 139​หมู่2 · บ้านกลาง/ Ban Klang</t>
+          <t>12ม.6ต.บางแก้ว</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>795136862111045</t>
+          <t>800152733254698</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SP2-001703</t>
+          <t>PR5-000573</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BROTHER INK Cartridge BT-D60BK หมึกพิมพ์ SP2-001703</t>
+          <t>HP Smart Tank 515 AiO Printer / 1TJ09A (2Y*) (PR5-000573) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>280</v>
+        <v>3490</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>280</v>
+        <v>3490</v>
       </c>
       <c r="H45" t="n">
         <v>-0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -5155,47 +5151,51 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>ปฐม​ ชัยชนะ</t>
+          <t>สว่างวรรณ บุตรนาค</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>โรงเรียนอนุบาลเพลงพิณ​ 95/40​ ม.6​ ต.มะเร็ต​</t>
+          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>เกาะสมุย/ Ko Samui</t>
+          <t>เมืองนนทบุรี/ Mueang Nonthaburi</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>สุราษฎร์ธานี/ Surat Thani</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>84310</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr"/>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>3120100492162</t>
+        </is>
+      </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>660966535593</t>
+          <t>660891116186</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>ปฐม ชัยชนะ</t>
+          <t>สว่างวรรณ บุตรนาค</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>280</v>
+        <v>3490</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>24 Dec 2023 14:43</t>
+          <t>24 Dec 2023 16:16</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
@@ -5204,42 +5204,42 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>โรงเรียนอนุบาลเพลงพิณ​ 95/40​ ม.6​ ต.มะเร็ต​</t>
+          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>795168489704309</t>
+          <t>800173538628211</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ME6-000876</t>
+          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
+          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>155</v>
+        <v>680</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>155</v>
+        <v>680</v>
       </c>
       <c r="H46" t="n">
         <v>-0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -5259,91 +5259,91 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>นาย สอาด อินท์นัอย</t>
+          <t>สมาน  สบตุ๋ย</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>54/4 ม.2 ต.หาดทรายรี อ.เมือง จ.ชุมพร 86120</t>
+          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>เมืองชุมพร/ Mueang Chumphon</t>
+          <t>บางนา/ Bang Na</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>ชุมพร/ Chumphon</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>86120</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
-          <t>660946404392</t>
+          <t>660878176408</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>0801096035</t>
+          <t>สมาน</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>155</v>
+        <v>680</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>24 Dec 2023 16:14</t>
+          <t>24 Dec 2023 17:21</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>54/4 ม.2 ต.หาดทรายรี อ.เมือง จ.ชุมพร 86120</t>
+          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>795193009416184</t>
+          <t>800178151179981</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MNL-001916</t>
+          <t>PR1-000610</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
+          <t>EPSON Printer L121/C11CD76501  เครื่องพิมพ์แท็งค์แท้ (PR1-000610) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6990</v>
+        <v>2990</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>6990</v>
+        <v>2990</v>
       </c>
       <c r="H47" t="n">
         <v>-0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -5363,47 +5363,47 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>รชานนท์  โชติบุตร</t>
+          <t>อั้น in คราม</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>joy บ้านเลขที่99/24 หมู่ 2, ซอยวัดลำโพ, ต.ลำโพ</t>
+          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>บางบัวทอง/ Bang Bua Thong</t>
+          <t>บางกะปิ/ Bang Kapi</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
-          <t>660819250822</t>
+          <t>660893549874</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>0819250822</t>
+          <t>Prawit Saiyard</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>6990</v>
+        <v>2990</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>24 Dec 2023 17:07</t>
+          <t>24 Dec 2023 17:42</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
@@ -5412,42 +5412,42 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>joy บ้านเลขที่99/24 หมู่ 2, ซอยวัดลำโพ, ต.ลำโพ</t>
+          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>795193882369576</t>
+          <t>800185367747863</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PR5-000612</t>
+          <t>ME6-000875</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Epson EcoTank L4260 A4 Wi-Fi Duplex All-in-One Ink Tank Printer (Print/Copy/Scan/WiFi-Direct)(PR5-000612) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6890</v>
+        <v>109</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>6890</v>
+        <v>218</v>
       </c>
       <c r="H48" t="n">
         <v>-0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -5467,91 +5467,91 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>สะฝีย้ะ สำลี</t>
+          <t>อานันท์  แก้วคำมา</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>22/1หมู่4 ต คุระ อ คุระบุรี จ พังงา</t>
+          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>คุระบุรี/ Khura Buri</t>
+          <t>เถิน/ Thoen</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>พังงา/ Phang Nga</t>
+          <t>ลำปาง/ Lampang</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>82150</t>
+          <t>52160</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
-          <t>660936749745</t>
+          <t>660818852780</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>ซาฟีย๊ะห์ สำลี</t>
+          <t>Maemoksat</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>6890</v>
+        <v>218</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>24 Dec 2023 17:46</t>
+          <t>24 Dec 2023 18:14</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>22/1หมู่4 ต คุระ อ คุระบุรี จ พังงา</t>
+          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>795205459559120</t>
+          <t>800216973475656</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WIH-000001</t>
+          <t>SP2-001753</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WISE หูฟังมีสาย Type-C Stereo Earphones (HS-500) (WIH-000001)</t>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>299</v>
+        <v>1103</v>
       </c>
       <c r="H49" t="n">
         <v>-0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -5571,47 +5571,52 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>ชชาติ จันทร์ทอง</t>
+          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>345 อาคารซีพีทาวเวอร์ ถนนพัฒนาการคูขวาง ตำบลในเมือง · ในเมือง/ Nai Mueang</t>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>เมืองนครศรีธรรมราช/ Mueang Nakhon Si Thammarat</t>
+          <t>ปากเกร็ด/ Pak Kret</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>นครศรีธรรมราช/ Nakhon Si Thammarat</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>80000</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr"/>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0125566004236
+</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>660879060002</t>
+          <t>660936415666</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>ชชาติ จันทร์ทอง</t>
+          <t>weerapat Nimanong</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>299</v>
+        <v>1103</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>24 Dec 2023 18:08</t>
+          <t>24 Dec 2023 19:44</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -5620,42 +5625,42 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>345 อาคารซีพีทาวเวอร์ ถนนพัฒนาการคูขวาง ตำบลในเมือง · ในเมือง/ Nai Mueang</t>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>795242894233004</t>
+          <t>800216973475656</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>SP2-001755</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
+          <t>CANON Ink CL-57 CO หมึกพิมพ์ (SP2-001755) SP2-001755</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>120</v>
+        <v>545</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>600</v>
+        <v>1103</v>
       </c>
       <c r="H50" t="n">
         <v>-0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -5675,95 +5680,96 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>มัลลิกา แก้วพาณิชย์</t>
+          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>โรงสีย่งเส็ง 5 (บ้านชี) 142 ม.1</t>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>บ้านหมี่/ Ban Mi</t>
+          <t>ปากเกร็ด/ Pak Kret</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>ลพบุรี/ Lopburi</t>
+          <t>นนทบุรี/ Nonthaburi</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>15180</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr"/>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0125566004236
+</t>
+        </is>
+      </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>660899958533</t>
+          <t>660936415666</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>มัลลิกา แก้วพาณิชย์</t>
+          <t>weerapat Nimanong</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>600</v>
+        <v>1103</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>24 Dec 2023 20:07</t>
+          <t>24 Dec 2023 19:44</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>โรงสีย่งเส็ง 5 (บ้านชี) 142 ม.1</t>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>795306823750355</t>
+          <t>800260379788783</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SP2-001617</t>
+          <t>ME6-000970</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HP GT52 Ink Bottle Y MOH56AA SP2-001617</t>
+          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>245</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>สี:สีเหลือง</t>
-        </is>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="H51" t="n">
         <v>-0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -5783,91 +5789,91 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>ปริยกร ศรีลา</t>
+          <t>Hytham Kaddurah</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>358-360 หมู่ 5 ถนนซุปเปอร์ไฮเวย์ เชียงใหม่-ลำปาง ตำบลป่าตั</t>
+          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
+          <t>บางละมุง/ Bang Lamung</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>ชลบุรี/ Chonburi</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>50300</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
-          <t>660806711807</t>
+          <t>660969847039</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Khongfang Pariya</t>
+          <t>Hytham</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>245</v>
+        <v>299</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>24 Dec 2023 22:40</t>
+          <t>24 Dec 2023 21:20</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>358-360 หมู่ 5 ถนนซุปเปอร์ไฮเวย์ เชียงใหม่-ลำปาง ตำบลป่าตั</t>
+          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>799522751592186</t>
+          <t>800264598105304</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PR5-000548</t>
+          <t>SP2-001753</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CANON PIXMA G3010 ปริ้นเตอร์อิ๊งค์เจ็ต(PR5-000548) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3450</v>
+        <v>279</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>3450</v>
+        <v>558</v>
       </c>
       <c r="H52" t="n">
         <v>-0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ready_to_ship</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -5887,91 +5893,91 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Iakubovskii Igor</t>
+          <t>จุฑารัตน์ สุกกรี</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>267, 150 Phra Tam Nak 4 Alley, Pattaya 201 2 floor</t>
+          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>บางละมุง/ Bang Lamung</t>
+          <t>เมืองชุมพร/ Mueang Chumphon</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>ชลบุรี/ Chonburi</t>
+          <t>ชุมพร/ Chumphon</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>86190</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
-          <t>660948763017</t>
+          <t>660630609279</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>948763017</t>
+          <t>จุฑารัตน์</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>3450</v>
+        <v>558</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>23 Dec 2023 01:35</t>
+          <t>24 Dec 2023 21:35</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>267, 150 Phra Tam Nak 4 Alley, Pattaya 201 2 floor</t>
+          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>799536589885075</t>
+          <t>800288100533275</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ME6-000970</t>
+          <t>MS4-000931</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
+          <t>SANDISK Extreme SDSSDE61 Portable SSD 1TB (Sky-Blue color) MS4-000931</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>299</v>
+        <v>2990</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>299</v>
+        <v>2990</v>
       </c>
       <c r="H53" t="n">
         <v>-0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -5984,103 +5990,91 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>สาขาย่อย</t>
+          <t>สำนักงานใหญ่</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>บริษัทเทรลเฮดจำกัด</t>
+          <t>อนุชิต ไตรอรุณ</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>บริษัทเทรลเฮด จำกัด 48-50 ซอย1 ถ.พระปกเกล้า ต.พระสิงห์ อ.เมืองเชียงใหม่ จ. เชียงใหม่ 50200 โทร: 052-089-693, 095-538-0202 เลขประจำตัวเสียภาษี :0-1055-57176</t>
+          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
-          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
+          <t>ลำลูกกา/ Lam Luk Ka</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>ปทุมธานี/ Pathum Thani</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>50200</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>0-1055-57176-20-8</t>
-        </is>
-      </c>
+          <t>12150</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
-          <t>660955380202</t>
+          <t>660865654708</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Ahkom Laycher</t>
+          <t>anuchit traiaroon</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>299</v>
+        <v>2990</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>23 Dec 2023 05:17</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00001</t>
-        </is>
-      </c>
+          <t>24 Dec 2023 22:02</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>บริษัทเทรลเฮด จำกัด 48-50 ซอย1 ถ.พระปกเกล้า ต.พระสิงห์ อ.เมืองเชียงใหม่ จ. เชียงใหม่ 50200 โทร: 052-089-693, 095-538-0202 เลขประจำตัวเสียภาษี :0-1055-57176</t>
+          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>799561914268343</t>
+          <t>800290334435407</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SP2-001611</t>
+          <t>SP2-001753</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CANON Ink Bottle GI-790 Cyan SP2-001611</t>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>250</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>สี:Cyan</t>
-        </is>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="H54" t="n">
         <v>-0</v>
@@ -6107,91 +6101,91 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>เนืองนิตร ไชยคำภา</t>
+          <t>กัญญ์ณณัฏฐ์ สุริยะฉาย</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>49/29 ซอยเทพกุญชร 42 ต.คลองหนึ่ง</t>
+          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>คลองหลวง/ Khlong Luang</t>
+          <t>บึงกุ่ม/ Bueng Kum</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
-          <t>660860969308</t>
+          <t>660806315727</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>ยินดี ยิ้มสวย</t>
+          <t>Kannanat Suriyachai</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>250</v>
+        <v>279</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>23 Dec 2023 07:26</t>
+          <t>24 Dec 2023 22:24</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>49/29 ซอยเทพกุญชร 42 ต.คลองหนึ่ง</t>
+          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>799570305150341</t>
+          <t>800302183049682</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MS2-000960</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen1 DataTraveler Exodia Onyx MS2-000960</t>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>135</v>
+        <v>1860</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>135</v>
+        <v>1860</v>
       </c>
       <c r="H55" t="n">
         <v>-0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -6211,91 +6205,91 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>ดาราธิป ประมาโส</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>197 ม.10 ต.ท่าไห</t>
+          <t>1/174 Lalisa Moo9 Thawangtan</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>เขื่องใน/ Khueang Nai</t>
+          <t>สารภี/ Saraphi</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>อุบลราชธานี/ Ubon Ratchathani</t>
+          <t>เชียงใหม่/ Chiang Mai</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
-          <t>660843412219</t>
+          <t>660932824520</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>ดาราธิป ประมาโส</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>135</v>
+        <v>1860</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>23 Dec 2023 07:56</t>
+          <t>24 Dec 2023 23:30</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>197 ม.10 ต.ท่าไห</t>
+          <t>1/174 Lalisa Moo9 Thawangtan</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>799573517054688</t>
+          <t>800308146152775</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ME6-000916</t>
+          <t>MS2-000845</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSD Canvas GO Plus 64GB 170/70MB/s ME6-000916</t>
+          <t>SANDISK USB2.0 Cruzer Blade 32GB MS2-000845</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="H56" t="n">
         <v>-0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>delivered</t>
+          <t>packed</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -6315,84 +6309,84 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ชิติพัทธ์  สิริอมรกิจ</t>
+          <t>ปิยวัจณ์ ยศเมฆ</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>52 ซอยสังคมสงเคราะห์14 ถนนสังคมสงเคราะห์</t>
+          <t>43/2 ม.3 ต.เลม็ด อ.ไชยา จ.สุราษฎร์ธานี</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>ลาดพร้าว/ Lad Phraw</t>
+          <t>ไชยา/ Chaiya</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>สุราษฎร์ธานี/ Surat Thani</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>84110</t>
         </is>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
-          <t>66898214664</t>
+          <t>660902138035</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>ชิติพัทธ์  สิริอมรกิจ</t>
+          <t>Piyawat Yotmet</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>23 Dec 2023 08:11</t>
+          <t>24 Dec 2023 23:37</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>52 ซอยสังคมสงเคราะห์14 ถนนสังคมสงเคราะห์</t>
+          <t>43/2 ม.3 ต.เลม็ด อ.ไชยา จ.สุราษฎร์ธานี</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>799640781853571</t>
+          <t>800321509632607</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MS2-000960</t>
+          <t>MNL-001916</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen1 DataTraveler Exodia Onyx MS2-000960</t>
+          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>135</v>
+        <v>6990</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>135</v>
+        <v>6990</v>
       </c>
       <c r="H57" t="n">
         <v>-0</v>
@@ -6419,84 +6413,84 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>นายณัฐวัฒน์ ศิริโสภาพงษ์</t>
+          <t>ขวัญชัย ศิริสุข</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ร้านยี่สิบค้าวัสดุ 81/8 ม.2 ต.ดอนเกาะกา อ.บางน้ำเปรี้ยว จ.ฉะเชิงเทรา</t>
+          <t>หมู่ 6 ท่าตูม 173/2</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>บางน้ำเปรี้ยว/ Bang Nam Priao</t>
+          <t>ศรีมหาโพธิ/ Si Maha Phot</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>ฉะเชิงเทรา/ Chachoengsao</t>
+          <t>ปราจีนบุรี/ Prachin Buri</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
-          <t>660627251757</t>
+          <t>660863245964</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>นายณัฐวัฒน์ ศิริโสภาพงษ์</t>
+          <t>Khwanchai Sirisuk</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>135</v>
+        <v>6990</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>23 Dec 2023 11:25</t>
+          <t>25 Dec 2023 00:09</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>ร้านยี่สิบค้าวัสดุ 81/8 ม.2 ต.ดอนเกาะกา อ.บางน้ำเปรี้ยว จ.ฉะเชิงเทรา</t>
+          <t>หมู่ 6 ท่าตูม 173/2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>799651316207084</t>
+          <t>800350722394774</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MS2-000904</t>
+          <t>MS4-000826</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KINGSTON USB3.2 Gen1 DTX 64GB/5Y MS2-000904</t>
+          <t>SANDISK Extreme SDSSDE61 Portable SSD 2TB MS4-000826</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>135</v>
+        <v>4990</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>270</v>
+        <v>4990</v>
       </c>
       <c r="H58" t="n">
         <v>-0</v>
@@ -6523,47 +6517,47 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>นราภรณ์ ไชยสิงห์</t>
+          <t>นวัช ทัฬหิกรณ์</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>หอต้นกล้ากะต้นน้ำ​ 160 หมู่​ 8​ ตำบลท่าม่วง​ อำเภอเสลภูมิ​ จังหวัดร้อยเอ็ด​ 4512</t>
+          <t>55 อาคาร เอ.เอ.แคปปิตอลรัชดา ถ.รัชดาภิเษก ชั้น7</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>เสลภูมิ/ Selaphum</t>
+          <t>ดินแดง/ Din Daeng</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>ร้อยเอ็ด/ Roi Et</t>
+          <t>กรุงเทพมหานคร/ Bangkok</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>45120</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
-          <t>660653032359</t>
+          <t>660801491424</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>นราภรณ์ ไชยสิงห์</t>
+          <t>ntunhikorn</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>270</v>
+        <v>4990</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>23 Dec 2023 11:21</t>
+          <t>25 Dec 2023 02:05</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
@@ -6572,35 +6566,35 @@
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>หอต้นกล้ากะต้นน้ำ​ 160 หมู่​ 8​ ตำบลท่าม่วง​ อำเภอเสลภูมิ​ จังหวัดร้อยเอ็ด​ 4512</t>
+          <t>55 อาคาร เอ.เอ.แคปปิตอลรัชดา ถ.รัชดาภิเษก ชั้น7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>799676353195348</t>
+          <t>800397746150140</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AC7-000864</t>
+          <t>GMA-001466</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LUMIRA ปลั๊กไฟ 5 สวิตซ์ 5 ช่อง 3M. LS-805 (3Y) (AC7-000864)</t>
+          <t>LOGA GAMING SWITCH MECHANICAL SWITCHES : NOMYEN LINEAR 35 PCS (GMA-001466)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H59" t="n">
         <v>-0</v>
@@ -6627,51 +6621,47 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Teawapol Boonyam</t>
+          <t>ปรเมศร์ ป้องไฝ</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>89/263 หมู่ที่ 6 ถ.เสมาฟ้าคราม ต.คูคต</t>
+          <t>หอพักรุ่งแสงทอง 97 ,หมูู่10 ,ถนนพหลโยธิน หอพักรุ้งแสงทอง อาคารA ชั้น3 · ทรายขาว/ Sai Khao</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>ลำลูกกา/ Lam Luk Ka</t>
+          <t>พาน/ Phan</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
+          <t>เชียงราย/ Chiang Rai</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>12130</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>1139600362618</t>
-        </is>
-      </c>
+          <t>57120</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
         <is>
-          <t>660829713552</t>
+          <t>660821609308</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Teawapol Boonyam</t>
+          <t>ปรเมศร์ ป้องไฝ</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>23 Dec 2023 12:41</t>
+          <t>25 Dec 2023 08:14</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
@@ -6680,42 +6670,46 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>89/263 หมู่ที่ 6 ถ.เสมาฟ้าคราม ต.คูคต</t>
+          <t>หอพักรุ่งแสงทอง 97 ,หมูู่10 ,ถนนพหลโยธิน หอพักรุ้งแสงทอง อาคารA ชั้น3 · ทรายขาว/ Sai Khao</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>799681763683030</t>
+          <t>800420111896380</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MS2-000944</t>
+          <t>GMP-000142</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
+          <t>RAZER MOUSE PAD GOLIATHUS CHROMA EXTENDED GMP-000142</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>135</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>2190</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Color Family:Black</t>
+        </is>
+      </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>135</v>
+        <v>2190</v>
       </c>
       <c r="H60" t="n">
         <v>-0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -6735,3341 +6729,60 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ประภาพรรณ จันทรรวงทอง</t>
+          <t>Sun Shenghuai</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>137/1-3 ม.1 ถนน สีคิ้ว-ชัยภูมิ ต.สีคิ้ว อ.สีคิ้ว</t>
+          <t>Room 132, BFC 1, 187/3 บางวัว 4 Bang Wua, Bang Pakong District, Chachoengsao 24180  132</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>สีคิ้ว/ Sikhio</t>
+          <t>บางปะกง/ Bang Pakong</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>นครราชสีมา/ Nakhon Ratchasima</t>
+          <t>ฉะเชิงเทรา/ Chachoengsao</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>30140</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr"/>
+          <t>24130</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>0-993-0004-6770-1</t>
+        </is>
+      </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>660898467307</t>
+          <t>660909087666</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>ปุณณ์🚀🌌</t>
+          <t>909087666</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>135</v>
+        <v>2190</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>23 Dec 2023 13:04</t>
+          <t>25 Dec 2023 08:59</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>137/1-3 ม.1 ถนน สีคิ้ว-ชัยภูมิ ต.สีคิ้ว อ.สีคิ้ว</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>799723992597826</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>PR5-000627</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>CANON PIXMA E4570 (PR5-000627) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2590</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="n">
-        <v>2590</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Unpaid</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>บุญญมาลย์ นันต๊ะเหล็ก</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>43/3 ม.4 ต.บ้านกล้วย อ.เมือง</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>เมืองสุโขทัย/ Mueang Sukhothai</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>สุโขทัย/ Sukhothai</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>64000</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>3640100570118</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>660610802912</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>บุญญมาลย์ นันต๊ะเหล็ก</t>
-        </is>
-      </c>
-      <c r="Z61" t="n">
-        <v>2590</v>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 14:58</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>43/3 ม.4 ต.บ้านกล้วย อ.เมือง</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>799734548616425</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>PR5-000548</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CANON PIXMA G3010 ปริ้นเตอร์อิ๊งค์เจ็ต(PR5-000548) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>3450</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>3450</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>เอ็ม เจ โมเดิร์น คอม โดย นายธงชัย ทองสุขแสง</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>เลขที่ 135/99 อาคารตึกคอมศรีราชา ห้อง3BS20,317 ชั้น3 ถ.สุขุมวิท  ต.ศรีราชา</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>ศรีราชา/ Si Racha</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>ชลบุรี/ Chonburi</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>20110</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>3130100532563</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>660972130231</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>Noon</t>
-        </is>
-      </c>
-      <c r="Z62" t="n">
-        <v>3450</v>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 15:04</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>เลขที่ 135/99 อาคารตึกคอมศรีราชา ห้อง3BS20,317 ชั้น3 ถ.สุขุมวิท  ต.ศรีราชา</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>799757949112069</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>PR5-000582</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>1860</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1860</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>สิริญาพร อุ่นต้าว</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>229 หมู่ 5 ตำบลท่าข้าม สำนักงานเทศบาลตำบลท่าข้าม</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>เวียงแก่น/ Wiang Kaen</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>เชียงราย/ Chiang Rai</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>57310</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>660649789935</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>Siriyaporn Auntao</t>
-        </is>
-      </c>
-      <c r="Z63" t="n">
-        <v>1860</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 16:21</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="n">
-        <v>24</v>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>229 หมู่ 5 ตำบลท่าข้าม สำนักงานเทศบาลตำบลท่าข้าม</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>799778380669239</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MS2-000870</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>SANDISK Ultra Dual Drive Go USB Type-C Flash Drive, SDDDC3 512GB</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>1490</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>1490</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>บริษัท เอสเคซี เอ็นจิเนียริ่ง จำกัด</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>เลขประจำตัวผู้เสียภาษี 0105555137272 สำนักงานใหญ่ เลขที่ 88/259 หมู่ที่ 7 ตำบลบางคูเวียง</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>บางกรวย/ Bang Kruai</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>11130</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>0105555137272</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>660889046666</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>วฤณดา เจริญพานนท์</t>
-        </is>
-      </c>
-      <c r="Z64" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 17:40</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>เลขประจำตัวผู้เสียภาษี 0105555137272 สำนักงานใหญ่ เลขที่ 88/259 หมู่ที่ 7 ตำบลบางคูเวียง</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>799837705953857</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>MS2-000944</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>135</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="n">
-        <v>135</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>ศิริรัตน์  จันทร์ศิริมลกุล</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>148/48 ถนนวิสุทธิกษัตริย์ ซอยวิเศษไชยชาญ ตำบลในเมือง</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>เมืองพิษณุโลก/ Mueang Phitsanulok</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>พิษณุโลก/ Phitsanulok</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>65000</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>660877319653</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>ศิริรัตน์  จันทร์ศิริมลกุล</t>
-        </is>
-      </c>
-      <c r="Z65" t="n">
-        <v>135</v>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 19:56</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr"/>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>148/48 ถนนวิสุทธิกษัตริย์ ซอยวิเศษไชยชาญ ตำบลในเมือง</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>799866535413650</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>MS2-000964</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>SanDisk Ultra Shift USB 3.2 Gen 1 Flash Drive, CZ410 32GB,Evening Primrose (Green) MS2-000964</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>129</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>387</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>ปรารถนา พรวรากรณ์</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>7 ซ.รามคำแหง 118 แยก 83 ถ.สุขาภิบาล3 สะพานสูง</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>สะพานสูง/ Sapan Sung</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3100601187389
-</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>660813610969</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>ปรารถนา พรวรากรณ์</t>
-        </is>
-      </c>
-      <c r="Z66" t="n">
-        <v>387</v>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 21:26</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr"/>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>7 ซ.รามคำแหง 118 แยก 83 ถ.สุขาภิบาล3 สะพานสูง</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>799866535413650</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MS2-000969</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>SanDisk Ultra Shift USB 3.2 Gen 1 Flash Drive, CZ410 32GB,Bachelor Button (Blue) MS2-000969</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>129</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>387</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>ปรารถนา พรวรากรณ์</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>7 ซ.รามคำแหง 118 แยก 83 ถ.สุขาภิบาล3 สะพานสูง</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>สะพานสูง/ Sapan Sung</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3100601187389
-</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>660813610969</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>ปรารถนา พรวรากรณ์</t>
-        </is>
-      </c>
-      <c r="Z67" t="n">
-        <v>387</v>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 21:26</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr"/>
-      <c r="AC67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>7 ซ.รามคำแหง 118 แยก 83 ถ.สุขาภิบาล3 สะพานสูง</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>799866535413650</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MS2-000973</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SanDisk Ultra Shift USB 3.2 Gen 1 Flash Drive, CZ410 32GB,Cattleya Orchid (Purple) MS2-000973</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>129</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>387</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>ปรารถนา พรวรากรณ์</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>7 ซ.รามคำแหง 118 แยก 83 ถ.สุขาภิบาล3 สะพานสูง</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>สะพานสูง/ Sapan Sung</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3100601187389
-</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>660813610969</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>ปรารถนา พรวรากรณ์</t>
-        </is>
-      </c>
-      <c r="Z68" t="n">
-        <v>387</v>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 21:26</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr"/>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>7 ซ.รามคำแหง 118 แยก 83 ถ.สุขาภิบาล3 สะพานสูง</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>799868147905563</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>PR5-000547</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Canon เครื่องพิมพ์อิงค์เจ็ท PIXMA มัลติฟังค์ชั่น 3 IN 1 รุ่น G2010 *พร้อมหมึกแท้ในกล่อง 1 ชุด* (PR5-000547)</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>3250</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>3250</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>ทิพย์สุคนธ์</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>โรงเรียนบ้านปางสุด หมู่ 12 ต.แม่เล่ย์</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>แม่วงก์/ Mae Wong</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>นครสวรรค์/ Nakhon Sawan</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>60150</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>1659900275830</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>660619591999</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>Thipsukhon Khawiam</t>
-        </is>
-      </c>
-      <c r="Z69" t="n">
-        <v>3250</v>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>23 Dec 2023 21:29</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr"/>
-      <c r="AC69" t="n">
-        <v>50</v>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>โรงเรียนบ้านปางสุด หมู่ 12 ต.แม่เล่ย์</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>799929924712449</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>SP2-1713+SP2-1714+SP2-1715+SP2-1716</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Epson หมึกแท้รุ่น T00V (003) Ink Bottle Set 4 สี (SP2-1713+SP2-1714+SP2-1715+SP2-1716)</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>800</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>800</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Zaw Min Tun</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>คลองเตย/ Khlong Toei</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>10110</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>660829623134</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>JH Aung Aung</t>
-        </is>
-      </c>
-      <c r="Z70" t="n">
-        <v>800</v>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 01:32</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr"/>
-      <c r="AC70" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>799930194244423</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>ME6-000876</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>155</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>155</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>ภูษิต  ปาปะเก</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>เมืองสมุทรปราการ/ Mueang Samut Prakan</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>สมุทรปราการ/ Samut Prakan</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>10280</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>660890528126</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>ภูษิต  ปาปะเก</t>
-        </is>
-      </c>
-      <c r="Z71" t="n">
-        <v>155</v>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 03:33</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr"/>
-      <c r="AC71" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>799963152618334</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>ME6-000960</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>SanDisk Ultra microSDXC, SQUAB 64GB, A1, C10, U1, UHS-I, 140MB/s R, 4x6, 10Y</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>195</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>195</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>อังษณา พรมทัณ</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>ดุสิต/ Dusit</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>10300</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>1103700155899</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>660898881040</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>อังษณา พรมทัณ</t>
-        </is>
-      </c>
-      <c r="Z72" t="n">
-        <v>195</v>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 07:45</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr"/>
-      <c r="AC72" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>799969900750744</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>MS2-000944</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>135</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>135</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>รพีพงศ์ ศศิธรวัณณ์</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>เมืองนนทบุรี/ Mueang Nonthaburi</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>11000</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>660982523524</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>Reaw</t>
-        </is>
-      </c>
-      <c r="Z73" t="n">
-        <v>135</v>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 07:46</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr"/>
-      <c r="AC73" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>799979507148952</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>IP7-001199</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>LOGITECH COMBO TOUCH FOR iPAD 10th GENERATION (1Y) IP7-001199 (จำนวนจำกัด)</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>3790</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>3790</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>packed</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>HADIN</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>198/4, Moo 10</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>หางดง/ Hang Dong</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>50230</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>660828210693</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>Mehdi Hadim</t>
-        </is>
-      </c>
-      <c r="Z74" t="n">
-        <v>3790</v>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 08:21</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr"/>
-      <c r="AC74" t="n">
-        <v>47</v>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>198/4, Moo 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>800009590366429</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>SP4-000302</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>120</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="n">
-        <v>2</v>
-      </c>
-      <c r="G75" t="n">
-        <v>240</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>มลฤดี  รู้รักตน</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>ปากเกร็ด/ Pak Kret</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>11120</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>0125537003979</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>660899910145</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>Monludee Rurakton</t>
-        </is>
-      </c>
-      <c r="Z75" t="n">
-        <v>240</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 10:12</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>800045958990703</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MNL-001862</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ACER LED Monitor EH200Qbi - 19.5"/TN/75Hz/3Y/MNL-001862</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1890</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1890</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>นายคณกฤช มัชฌิมา</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>เมืองพิจิตร/ Mueang Phichit</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>พิจิตร/ Phichit</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>66000</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>66899594344</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>นายคณกฤช  มัชฌิมา</t>
-        </is>
-      </c>
-      <c r="Z76" t="n">
-        <v>1890</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 11:35</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr"/>
-      <c r="AC76" t="n">
-        <v>53</v>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>800074729069035</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>PR5-000610</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>EPSON Printer L3210 STD/C11CJ68501 (PR5-000610) (จำกัดการซื้อ1ออเดอร์ไม่เกิน3เครื่อง) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>3730</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>3730</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>เฉลิม พรพงษ์</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>ธัญบุรี/ Thanyaburi</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>12130</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>1195703950</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>660838464600</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>Chaloem Phornphong</t>
-        </is>
-      </c>
-      <c r="Z77" t="n">
-        <v>3730</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 12:43</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr"/>
-      <c r="AC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>800085587433269</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>PR5-000582</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1860</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1860</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>สมภพ บูรณพิมพ์</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>บ้านบึง/ Ban Bueng</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>ชลบุรี/ Chonburi</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>20220</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>660894014557</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>*******874</t>
-        </is>
-      </c>
-      <c r="Z78" t="n">
-        <v>1860</v>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 13:30</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="n">
-        <v>59</v>
-      </c>
-      <c r="AD78" t="inlineStr">
-        <is>
-          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>800090726148364</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>MS2-000844</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>SANDISK USB2.0 Cruzer Blade 16GB MS2-000844</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>115</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="n">
-        <v>115</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>นาย จิรวัฒน์ อ่อนคล้าย</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>ตาคลี/ Takhli</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>นครสวรรค์/ Nakhon Sawan</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>60140</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>660814081091</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>0814081091</t>
-        </is>
-      </c>
-      <c r="Z79" t="n">
-        <v>115</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 13:23</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr"/>
-      <c r="AC79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD79" t="inlineStr">
-        <is>
-          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>800094782668343</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>PR5-000503</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CANON PIXMA E-410 Black</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1335</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Color Family:Black</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1335</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Ethel Joy</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>บางบัวทอง/ Bang Bua Thong</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>11110</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>660832393046</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>Ethel Joy</t>
-        </is>
-      </c>
-      <c r="Z80" t="n">
-        <v>1335</v>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 13:51</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD80" t="inlineStr">
-        <is>
-          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>800122510696050</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SP2-001753</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>279</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>279</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>ศิริกัญญา​ โต​เจริญ​</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>12ม.6ต.บางแก้ว</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>เมืองฉะเชิงเทรา/ Mueang Chachoengsao</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>ฉะเชิงเทรา/ Chachoengsao</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>24000</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>660819831278</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>ศิริกัญญา โตเจริญ</t>
-        </is>
-      </c>
-      <c r="Z81" t="n">
-        <v>279</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 14:40</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="n">
-        <v>38</v>
-      </c>
-      <c r="AD81" t="inlineStr">
-        <is>
-          <t>12ม.6ต.บางแก้ว</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>800152733254698</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PR5-000573</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HP Smart Tank 515 AiO Printer / 1TJ09A (2Y*) (PR5-000573) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>3490</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" t="n">
-        <v>3490</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>สว่างวรรณ บุตรนาค</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>เมืองนนทบุรี/ Mueang Nonthaburi</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>11000</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>3120100492162</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>660891116186</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>สว่างวรรณ บุตรนาค</t>
-        </is>
-      </c>
-      <c r="Z82" t="n">
-        <v>3490</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 16:16</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr"/>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>800173538628211</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>680</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>680</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>สมาน  สบตุ๋ย</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>บางนา/ Bang Na</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>10260</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>660878176408</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>สมาน</t>
-        </is>
-      </c>
-      <c r="Z83" t="n">
-        <v>680</v>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 17:21</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD83" t="inlineStr">
-        <is>
-          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>800178151179981</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>PR1-000610</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>EPSON Printer L121/C11CD76501  เครื่องพิมพ์แท็งค์แท้ (PR1-000610) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>2990</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="n">
-        <v>2990</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>อั้น in คราม</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>บางกะปิ/ Bang Kapi</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>660893549874</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Prawit Saiyard</t>
-        </is>
-      </c>
-      <c r="Z84" t="n">
-        <v>2990</v>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 17:42</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr"/>
-      <c r="AC84" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>800185367747863</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>ME6-000875</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>109</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" t="n">
-        <v>218</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>อานันท์  แก้วคำมา</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>เถิน/ Thoen</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>ลำปาง/ Lampang</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>52160</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>660818852780</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>Maemoksat</t>
-        </is>
-      </c>
-      <c r="Z85" t="n">
-        <v>218</v>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 18:14</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr"/>
-      <c r="AC85" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD85" t="inlineStr">
-        <is>
-          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>800216973475656</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>SP2-001753</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>279</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1103</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>ปากเกร็ด/ Pak Kret</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>11120</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0125566004236
-</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>660936415666</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>weerapat Nimanong</t>
-        </is>
-      </c>
-      <c r="Z86" t="n">
-        <v>1103</v>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 19:44</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr"/>
-      <c r="AC86" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>800216973475656</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>SP2-001755</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>CANON Ink CL-57 CO หมึกพิมพ์ (SP2-001755) SP2-001755</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>545</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="n">
-        <v>1103</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>ปากเกร็ด/ Pak Kret</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>นนทบุรี/ Nonthaburi</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>11120</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0125566004236
-</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>660936415666</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>weerapat Nimanong</t>
-        </is>
-      </c>
-      <c r="Z87" t="n">
-        <v>1103</v>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 19:44</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr"/>
-      <c r="AC87" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD87" t="inlineStr">
-        <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>800260379788783</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>ME6-000970</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>299</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" t="n">
-        <v>299</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Hytham Kaddurah</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>บางละมุง/ Bang Lamung</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>ชลบุรี/ Chonburi</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>20150</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>660969847039</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>Hytham</t>
-        </is>
-      </c>
-      <c r="Z88" t="n">
-        <v>299</v>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 21:20</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr"/>
-      <c r="AC88" t="n">
-        <v>38</v>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>800264598105304</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SP2-001753</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>279</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
-      <c r="G89" t="n">
-        <v>558</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>จุฑารัตน์ สุกกรี</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>เมืองชุมพร/ Mueang Chumphon</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>ชุมพร/ Chumphon</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>86190</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>660630609279</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>จุฑารัตน์</t>
-        </is>
-      </c>
-      <c r="Z89" t="n">
-        <v>558</v>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 21:35</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="n">
-        <v>38</v>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>800288100533275</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>MS4-000931</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SANDISK Extreme SDSSDE61 Portable SSD 1TB (Sky-Blue color) MS4-000931</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>2990</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2990</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>อนุชิต ไตรอรุณ</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>ลำลูกกา/ Lam Luk Ka</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>12150</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>660865654708</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>anuchit traiaroon</t>
-        </is>
-      </c>
-      <c r="Z90" t="n">
-        <v>2990</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 22:02</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr"/>
-      <c r="AC90" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>800290334435407</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>SP2-001753</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>279</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
-        <v>279</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>สำนักงานใหญ่</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>กัญญ์ณณัฏฐ์ สุริยะฉาย</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>บึงกุ่ม/ Bueng Kum</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>660806315727</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Kannanat Suriyachai</t>
-        </is>
-      </c>
-      <c r="Z91" t="n">
-        <v>279</v>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>24 Dec 2023 22:24</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr"/>
-      <c r="AC91" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD91" t="inlineStr">
-        <is>
-          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
+          <t>Room 132, BFC 1, 187/3 บางวัว 4 Bang Wua, Bang Pakong District, Chachoengsao 24180  132</t>
         </is>
       </c>
     </row>

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD60"/>
+  <dimension ref="A1:AD92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,7 +611,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -642,12 +642,12 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ห้วยขวาง/ Huai Khwang</t>
+          <t>ห้วยขวาง</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -750,12 +750,12 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>บางกรวย/ Bang Kruai</t>
+          <t>บางกรวย</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>นนทบุรี</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -854,12 +854,12 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ถลาง/ Thalang</t>
+          <t>ถลาง</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>ภูเก็ต/ Phuket</t>
+          <t>ภูเก็ต</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -958,12 +958,12 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
+          <t>เมืองเชียงใหม่</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>เชียงใหม่</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1062,12 +1062,12 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>พระนคร/ Phra Nakhon</t>
+          <t>พระนคร</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1166,12 +1166,12 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>โพนทอง/ Phon Thong</t>
+          <t>โพนทอง</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>ร้อยเอ็ด/ Roi Et</t>
+          <t>ร้อยเอ็ด</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1270,12 +1270,12 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>นาหม่อม/ Na Mom</t>
+          <t>นาหม่อม</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>สงขลา/ Songkhla</t>
+          <t>สงขลา</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1374,12 +1374,12 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>เมืองตรัง/ Mueang Trang</t>
+          <t>เมืองตรัง</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>ตรัง/ Trang</t>
+          <t>ตรัง</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1478,12 +1478,12 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ทุ่งครุ/ Thung Khru</t>
+          <t>ทุ่งครุ</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1582,12 +1582,12 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>สิงหนคร/ Singhanakhon</t>
+          <t>สิงหนคร</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>สงขลา/ Songkhla</t>
+          <t>สงขลา</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1686,12 +1686,12 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>เมืองกระบี่/ Mueang Krabi</t>
+          <t>เมืองกระบี่</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>กระบี่/ Krabi</t>
+          <t>กระบี่</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1790,12 +1790,12 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>จตุจักร/ Chatuchak</t>
+          <t>จตุจักร</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1894,12 +1894,12 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>จอมทอง/ Chom Thong</t>
+          <t>จอมทอง</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2006,12 +2006,12 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>คลองเตย/ Khlong Toei</t>
+          <t>คลองเตย</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2114,12 +2114,12 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>เมืองชลบุรี/ Mueang Chon Buri</t>
+          <t>เมืองชลบุรี</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>ชลบุรี/ Chonburi</t>
+          <t>ชลบุรี</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2218,12 +2218,12 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>อ่าวลึก/ Ao Luek</t>
+          <t>อ่าวลึก</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>กระบี่/ Krabi</t>
+          <t>กระบี่</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2322,12 +2322,12 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>เกาะสมุย/ Ko Samui</t>
+          <t>เกาะสมุย</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>สุราษฎร์ธานี/ Surat Thani</t>
+          <t>สุราษฎร์ธานี</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2426,12 +2426,12 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>เมืองชุมพร/ Mueang Chumphon</t>
+          <t>เมืองชุมพร</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>ชุมพร/ Chumphon</t>
+          <t>ชุมพร</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2530,12 +2530,12 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>บางบัวทอง/ Bang Bua Thong</t>
+          <t>บางบัวทอง</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>นนทบุรี</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2634,12 +2634,12 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>คุระบุรี/ Khura Buri</t>
+          <t>คุระบุรี</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>พังงา/ Phang Nga</t>
+          <t>พังงา</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -2738,12 +2738,12 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>เมืองนครศรีธรรมราช/ Mueang Nakhon Si Thammarat</t>
+          <t>เมืองนครศรีธรรมราช</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>นครศรีธรรมราช/ Nakhon Si Thammarat</t>
+          <t>นครศรีธรรมราช</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2842,12 +2842,12 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>บ้านหมี่/ Ban Mi</t>
+          <t>บ้านหมี่</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>ลพบุรี/ Lopburi</t>
+          <t>ลพบุรี</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2950,12 +2950,12 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
+          <t>เมืองเชียงใหม่</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>เชียงใหม่</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3054,12 +3054,12 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>ปทุมวัน/ Pathum Wan</t>
+          <t>ปทุมวัน</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -3158,12 +3158,12 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>บางบ่อ/ Bang Bo</t>
+          <t>บางบ่อ</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>สมุทรปราการ/ Samut Prakan</t>
+          <t>สมุทรปราการ</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3266,12 +3266,12 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>วังน้อย/ Wang Noi</t>
+          <t>วังน้อย</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>พระนครศรีอยุธยา/ Phra Nakhon Si Ayutthaya</t>
+          <t>พระนครศรีอยุธยา</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3374,12 +3374,12 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>วังน้อย/ Wang Noi</t>
+          <t>วังน้อย</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>พระนครศรีอยุธยา/ Phra Nakhon Si Ayutthaya</t>
+          <t>พระนครศรีอยุธยา</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3482,12 +3482,12 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>ห้วยขวาง/ Huai Khwang</t>
+          <t>ห้วยขวาง</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3586,12 +3586,12 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>เบตง/ Betong</t>
+          <t>เบตง</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>ยะลา/ Yala</t>
+          <t>ยะลา</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3690,12 +3690,12 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>เมืองเชียงใหม่/ Mueang Chiang Mai</t>
+          <t>เมืองเชียงใหม่</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>เชียงใหม่</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3735,35 +3735,35 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>799858548970134</t>
+          <t>795449850311731</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ME6-000914</t>
+          <t>ME6-000875</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KINGSTON SD Canvas GO Plus 64GB 170/70MB/s ME6-000914</t>
+          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>229</v>
+        <v>109</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>229</v>
+        <v>545</v>
       </c>
       <c r="H32" t="n">
         <v>-0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -3783,91 +3783,91 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>นายธนภัทร ผิวเงิน</t>
+          <t>รพี วงศ์สิทธิชัยกุล</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ร้านถ่ายรูปบ้านขาม 260 หมู่ 10 บ้านนาขาม ตำบลศรีชมภู</t>
+          <t>76 ซอย76 ถนนพระราม 2 แขวงแสมด</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>โซ่พิสัย/ So Phisai</t>
+          <t>บางขุนเทียน</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>บึงกาฬ/ Bueng Kan</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>38170</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>660957038298</t>
+          <t>660835105459</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>นายธนภัทร ผิวเงิน</t>
+          <t>MMMMMMJ</t>
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>229</v>
+        <v>545</v>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>25 Dec 2023 07:51</t>
+          <t>25 Dec 2023 10:04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>ร้านถ่ายรูปบ้านขาม 260 หมู่ 10 บ้านนาขาม ตำบลศรีชมภู</t>
+          <t>76 ซอย76 ถนนพระราม 2 แขวงแสมด</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>799929924712449</t>
+          <t>795463601277155</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SP2-1713+SP2-1714+SP2-1715+SP2-1716</t>
+          <t>MNL-001916</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Epson หมึกแท้รุ่น T00V (003) Ink Bottle Set 4 สี (SP2-1713+SP2-1714+SP2-1715+SP2-1716)</t>
+          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>800</v>
+        <v>6990</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="n">
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>800</v>
+        <v>6990</v>
       </c>
       <c r="H33" t="n">
         <v>-0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -3887,91 +3887,95 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Zaw Min Tun</t>
+          <t>รัฐศรันธ์ ปริสัญญุตานนท์</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
+          <t>19/70-71 หมู่ 7 คลองสาม คลองหลวง</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>คลองเตย/ Khlong Toei</t>
+          <t>คลองหลวง</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>ปทุมธานี</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>10110</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
+          <t>12120</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>0135566024903</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>660829623134</t>
+          <t>660814948859</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>JH Aung Aung</t>
+          <t>Ratsaran Parisanyutanon</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>800</v>
+        <v>6990</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>24 Dec 2023 01:32</t>
+          <t>25 Dec 2023 10:10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
+          <t>19/70-71 หมู่ 7 คลองสาม คลองหลวง</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>799930194244423</t>
+          <t>795464494525317</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ME6-000876</t>
+          <t>ME6-000875</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
+          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="H34" t="n">
         <v>-0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -3991,47 +3995,47 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>ภูษิต  ปาปะเก</t>
+          <t>นาย ศราวุธ บุญจรัส</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
+          <t>บ้านสุขศรีการ ตึกA เลขที่ 738/1 ชั้น7 ห้อง A705</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>เมืองสมุทรปราการ/ Mueang Samut Prakan</t>
+          <t>สวนหลวง</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>สมุทรปราการ/ Samut Prakan</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
-          <t>660890528126</t>
+          <t>660945810691</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>ภูษิต  ปาปะเก</t>
+          <t>Sarawut Boonjarus</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>24 Dec 2023 03:33</t>
+          <t>25 Dec 2023 10:41</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
@@ -4040,42 +4044,42 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
+          <t>บ้านสุขศรีการ ตึกA เลขที่ 738/1 ชั้น7 ห้อง A705</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>799963152618334</t>
+          <t>795471096201128</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ME6-000960</t>
+          <t>MS4-000940</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SanDisk Ultra microSDXC, SQUAB 64GB, A1, C10, U1, UHS-I, 140MB/s R, 4x6, 10Y</t>
+          <t>SANDISK SDSSDE30 Portable SSD 2TB (Read speed up to 800MB/s,) MS4-000940</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>195</v>
+        <v>3850</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>195</v>
+        <v>3850</v>
       </c>
       <c r="H35" t="n">
         <v>-0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -4095,51 +4099,47 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>อังษณา พรมทัณ</t>
+          <t>กิตติชัย ชินคีรี</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
+          <t>238/251 วินด์รัชโยธิน รัชดาภิเษก ลาดยาว</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>ดุสิต/ Dusit</t>
+          <t>จตุจักร</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>10300</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>1103700155899</t>
-        </is>
-      </c>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
-          <t>660898881040</t>
+          <t>660833073168</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>อังษณา พรมทัณ</t>
+          <t>kittichai chinkiri</t>
         </is>
       </c>
       <c r="Z35" t="n">
-        <v>195</v>
+        <v>3850</v>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>24 Dec 2023 07:45</t>
+          <t>25 Dec 2023 10:49</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
@@ -4148,42 +4148,42 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
+          <t>238/251 วินด์รัชโยธิน รัชดาภิเษก ลาดยาว</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>799969900750744</t>
+          <t>795478093384683</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MS2-000944</t>
+          <t>MS6-000169</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
+          <t>WD BLACK SN770 500GB M.2 2280 NVMe Gen4 (WDS500G3X0E) (5Y) MS6-000169</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>135</v>
+        <v>1390</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>135</v>
+        <v>1390</v>
       </c>
       <c r="H36" t="n">
         <v>-0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -4203,91 +4203,95 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>รพีพงศ์ ศศิธรวัณณ์</t>
+          <t>พัทธพล ทองนาค</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
+          <t>839/146 หมู่1 ซอย6 หมู่บ้านโฮมการ์เด้นวิลสุรนารายณ์ ต.บ้านเกาะ อ.เมือง</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>เมืองนนทบุรี/ Mueang Nonthaburi</t>
+          <t>เมืองนครราชสีมา</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>นครราชสีมา</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>11000</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr"/>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>1309900950459</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>660982523524</t>
+          <t>660821287434</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Reaw</t>
+          <t>Newz Pattapon</t>
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>135</v>
+        <v>1390</v>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>24 Dec 2023 07:46</t>
+          <t>25 Dec 2023 11:01</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
+          <t>839/146 หมู่1 ซอย6 หมู่บ้านโฮมการ์เด้นวิลสุรนารายณ์ ต.บ้านเกาะ อ.เมือง</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>799979507148952</t>
+          <t>795480023552297</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IP7-001199</t>
+          <t>MS6-000168</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LOGITECH COMBO TOUCH FOR iPAD 10th GENERATION (1Y) IP7-001199 (จำนวนจำกัด)</t>
+          <t>WD BLACK SN770 250GB M.2 2280 NVMe Gen4 (WDS250G3X0E) (5Y) MS6-000168</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3790</v>
+        <v>850</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>3790</v>
+        <v>850</v>
       </c>
       <c r="H37" t="n">
         <v>-0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -4307,91 +4311,91 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>HADIN</t>
+          <t>วนิดา การนุกูล</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>198/4, Moo 10</t>
+          <t>แฟลต  NR ลาดพร้าว 87 แยก 22 แขวง คลองเจ้าคุณสิงห์ เขต วังทองหลาง กทม · วังทองหลาง/ Wang Thonglang</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>หางดง/ Hang Dong</t>
+          <t>วังทองหลาง</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
-          <t>660828210693</t>
+          <t>660621404074</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>Mehdi Hadim</t>
+          <t>วนิดา การนุกูล</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>3790</v>
+        <v>850</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>24 Dec 2023 08:21</t>
+          <t>25 Dec 2023 10:38</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>198/4, Moo 10</t>
+          <t>แฟลต  NR ลาดพร้าว 87 แยก 22 แขวง คลองเจ้าคุณสิงห์ เขต วังทองหลาง กทม · วังทองหลาง/ Wang Thonglang</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>800009590366429</t>
+          <t>795480461985094</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SP4-000302</t>
+          <t>MS2-000944</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
+          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="H38" t="n">
         <v>-0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -4411,51 +4415,47 @@
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>มลฤดี  รู้รักตน</t>
+          <t>กฤติน เกษมสุข</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
+          <t>54/1 ซอยสุขสวัสดิ์ 30 แยก 4 แขวงบางปะกอก เขตราษฎร์บูรณะ กทม 10140</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>ปากเกร็ด/ Pak Kret</t>
+          <t>ราษฎร์บูรณะ</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>11120</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>0125537003979</t>
-        </is>
-      </c>
+          <t>10140</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>660899910145</t>
+          <t>660652622535</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Monludee Rurakton</t>
+          <t>กฤติน เกษมสุข</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>240</v>
+        <v>135</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>24 Dec 2023 10:12</t>
+          <t>25 Dec 2023 10:50</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
@@ -4464,42 +4464,42 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
+          <t>54/1 ซอยสุขสวัสดิ์ 30 แยก 4 แขวงบางปะกอก เขตราษฎร์บูรณะ กทม 10140</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>800045958990703</t>
+          <t>795513424585686</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MNL-001862</t>
+          <t>SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ACER LED Monitor EH200Qbi - 19.5"/TN/75Hz/3Y/MNL-001862</t>
+          <t>CANON Ink Bottle GI-71 หมึกพิมพ์ SP2-001792+SP2-001793+SP2-001794+SP2-001795</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1890</v>
+        <v>1000</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1890</v>
+        <v>1000</v>
       </c>
       <c r="H39" t="n">
         <v>-0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -4519,91 +4519,95 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>นายคณกฤช มัชฌิมา</t>
+          <t>อาจสิทธิ์ ยอดเยี่ยม</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
+          <t>ร้านดินสอ(สำนักงานใหญ่) 212-213 ม. 2 ต. กังแอน อ. ปราสาท</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>เมืองพิจิตร/ Mueang Phichit</t>
+          <t>ปราสาท</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>พิจิตร/ Phichit</t>
+          <t>สุรินทร์</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>66000</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
+          <t>32140</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>3320500663337</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>66899594344</t>
+          <t>660817252696</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>นายคณกฤช  มัชฌิมา</t>
+          <t>ardsit yodyiam</t>
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>1890</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>24 Dec 2023 11:35</t>
+          <t>25 Dec 2023 11:55</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
+          <t>ร้านดินสอ(สำนักงานใหญ่) 212-213 ม. 2 ต. กังแอน อ. ปราสาท</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>800074729069035</t>
+          <t>795517684548610</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PR5-000610</t>
+          <t>MS2-000739</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EPSON Printer L3210 STD/C11CJ68501 (PR5-000610) (จำกัดการซื้อ1ออเดอร์ไม่เกิน3เครื่อง) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>SANDISK USB3.0 Ultra Flair CZ73 32GB MS2-000739</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3730</v>
+        <v>165</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>3730</v>
+        <v>165</v>
       </c>
       <c r="H40" t="n">
         <v>-0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -4623,51 +4627,48 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>เฉลิม พรพงษ์</t>
+          <t>กรวิท กาญจนะ</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
+          <t>214 ซ.บางแค7 เขตบางแค แขวงบางแค
+กทม. 10160</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>ธัญบุรี/ Thanyaburi</t>
+          <t>บางแค</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>12130</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>1195703950</t>
-        </is>
-      </c>
+          <t>10160</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
-          <t>660838464600</t>
+          <t>660837866475</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Chaloem Phornphong</t>
+          <t>gorawit gajana</t>
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>3730</v>
+        <v>165</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>24 Dec 2023 12:43</t>
+          <t>25 Dec 2023 12:24</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
@@ -4676,42 +4677,43 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
+          <t>214 ซ.บางแค7 เขตบางแค แขวงบางแค
+กทม. 10160</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>800085587433269</t>
+          <t>795536842553127</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>MS2-000905</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>KINGSTON USB3.2 Gen1 DTX 128GB/5Y MS2-000905</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1860</v>
+        <v>255</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>1860</v>
+        <v>510</v>
       </c>
       <c r="H41" t="n">
         <v>-0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -4731,91 +4733,91 @@
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>สมภพ บูรณพิมพ์</t>
+          <t>ทัศนีย์ กันภัย</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
+          <t>7/51 หมู่ 12 ซ.พันกสิกร(ซอยเจ้แฮ) ถ.จรดวิถีถ่อง ต.บ้านกล้วย</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>บ้านบึง/ Ban Bueng</t>
+          <t>เมืองสุโขทัย</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>ชลบุรี/ Chonburi</t>
+          <t>สุโขทัย</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>64000</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
-          <t>660894014557</t>
+          <t>660819153562</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>*******874</t>
+          <t>ทัศนีย์ กันภัย</t>
         </is>
       </c>
       <c r="Z41" t="n">
-        <v>1860</v>
+        <v>510</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>24 Dec 2023 13:30</t>
+          <t>25 Dec 2023 12:51</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
+          <t>7/51 หมู่ 12 ซ.พันกสิกร(ซอยเจ้แฮ) ถ.จรดวิถีถ่อง ต.บ้านกล้วย</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>800090726148364</t>
+          <t>795551859167833</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MS2-000844</t>
+          <t>MS2-000904</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SANDISK USB2.0 Cruzer Blade 16GB MS2-000844</t>
+          <t>KINGSTON USB3.2 Gen1 DTX 64GB/5Y MS2-000904</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H42" t="n">
         <v>-0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -4835,47 +4837,47 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>นาย จิรวัฒน์ อ่อนคล้าย</t>
+          <t>คณาธิป ปั้นจาด แผนกสารสนเทศ</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
+          <t>บริษัท กรุงไทยอาหาร จำกัด(มหาชน) 266 ม.11 ต.ในคลองบางปลากด</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>ตาคลี/ Takhli</t>
+          <t>พระสมุทรเจดีย์</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>นครสวรรค์/ Nakhon Sawan</t>
+          <t>สมุทรปราการ</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>60140</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
-          <t>660814081091</t>
+          <t>660838853884</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0814081091</t>
+          <t>Kanatip Panjard</t>
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>24 Dec 2023 13:23</t>
+          <t>25 Dec 2023 13:16</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
@@ -4884,46 +4886,42 @@
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
+          <t>บริษัท กรุงไทยอาหาร จำกัด(มหาชน) 266 ม.11 ต.ในคลองบางปลากด</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>800094782668343</t>
+          <t>795567433966029</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PR5-000503</t>
+          <t>MS2-000671</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CANON PIXMA E-410 Black</t>
+          <t>SANDISK USB3.0 Cruzer Glide CZ600 32GB MS2-000671</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1335</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Color Family:Black</t>
-        </is>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>1335</v>
+        <v>560</v>
       </c>
       <c r="H43" t="n">
         <v>-0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -4943,91 +4941,91 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Ethel Joy</t>
+          <t>baldacchino georges</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
+          <t>Green Habor Apartment 168/46-48 room401 Soi Nanairuamjai8 · ป่าตอง/ Pa Tong</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>บางบัวทอง/ Bang Bua Thong</t>
+          <t>กะทู้</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>ภูเก็ต</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>11110</t>
+          <t>83150</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
-          <t>660832393046</t>
+          <t>660937760692</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Ethel Joy</t>
+          <t>0937760692</t>
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>1335</v>
+        <v>560</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>24 Dec 2023 13:51</t>
+          <t>25 Dec 2023 13:41</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
+          <t>Green Habor Apartment 168/46-48 room401 Soi Nanairuamjai8 · ป่าตอง/ Pa Tong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>800122510696050</t>
+          <t>795580497730930</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>AC7-000893</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+          <t>PHILIPS ปลั๊กไฟ 5ช่อง 5สวิสต์ 5M (2Y) AC7-000893</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>279</v>
+        <v>519</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>279</v>
+        <v>519</v>
       </c>
       <c r="H44" t="n">
         <v>-0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -5047,91 +5045,91 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>ศิริกัญญา​ โต​เจริญ​</t>
+          <t>บุษฎี คงถาวร</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>12ม.6ต.บางแก้ว</t>
+          <t>285/61 ยูนิโอ สุขุมวิท 72 (เฟส 1 ล็อบบี้ตึก A)ซ.สุขุมวิท 72 ต.สำโรงเหนือ ตึก A เฟส 1</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>เมืองฉะเชิงเทรา/ Mueang Chachoengsao</t>
+          <t>เมืองสมุทรปราการ</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>ฉะเชิงเทรา/ Chachoengsao</t>
+          <t>สมุทรปราการ</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>24000</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>660819831278</t>
+          <t>660944892914</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>ศิริกัญญา โตเจริญ</t>
+          <t>Busadee Kongthavorn</t>
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>279</v>
+        <v>519</v>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>24 Dec 2023 14:40</t>
+          <t>25 Dec 2023 14:37</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>12ม.6ต.บางแก้ว</t>
+          <t>285/61 ยูนิโอ สุขุมวิท 72 (เฟส 1 ล็อบบี้ตึก A)ซ.สุขุมวิท 72 ต.สำโรงเหนือ ตึก A เฟส 1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>800152733254698</t>
+          <t>795601222200436</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PR5-000573</t>
+          <t>MS4-000825</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HP Smart Tank 515 AiO Printer / 1TJ09A (2Y*) (PR5-000573) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>SANDISK Extreme SDSSDE61 Portable SSD 1TB MS4-000825</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3490</v>
+        <v>2950</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
         <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>3490</v>
+        <v>2950</v>
       </c>
       <c r="H45" t="n">
         <v>-0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -5151,51 +5149,47 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>สว่างวรรณ บุตรนาค</t>
+          <t>Raman Antonau</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
+          <t>7/18 Soi Dara, Moo 2, 79/17 Building D, 2 Floor · กะทู้/ Kathu</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>เมืองนนทบุรี/ Mueang Nonthaburi</t>
+          <t>กะทู้</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>ภูเก็ต</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>11000</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>3120100492162</t>
-        </is>
-      </c>
+          <t>83120</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
-          <t>660891116186</t>
+          <t>660641231864</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>สว่างวรรณ บุตรนาค</t>
+          <t>R</t>
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>3490</v>
+        <v>2950</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>24 Dec 2023 16:16</t>
+          <t>25 Dec 2023 14:57</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
@@ -5204,42 +5198,42 @@
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
+          <t>7/18 Soi Dara, Moo 2, 79/17 Building D, 2 Floor · กะทู้/ Kathu</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>800173538628211</t>
+          <t>795614883492246</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+          <t>MS4-000939</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+          <t>SANDISK SDSSDE30 Portable SSD 1TB (Read speed up to 800MB/s,) MS4-000939</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>680</v>
+        <v>2250</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="H46" t="n">
         <v>-0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -5259,91 +5253,91 @@
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>สมาน  สบตุ๋ย</t>
+          <t>Artem</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
+          <t>9, หมู่ที่ 4 Muang Naka Rd · วิชิต/ Wichit</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>บางนา/ Bang Na</t>
+          <t>เมืองภูเก็ต</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>ภูเก็ต</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>10260</t>
+          <t>83000</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
-          <t>660878176408</t>
+          <t>660991876748</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>สมาน</t>
+          <t>Артём</t>
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>680</v>
+        <v>4500</v>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>24 Dec 2023 17:21</t>
+          <t>25 Dec 2023 15:57</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
+          <t>9, หมู่ที่ 4 Muang Naka Rd · วิชิต/ Wichit</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>800178151179981</t>
+          <t>795618258036120</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PR1-000610</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>EPSON Printer L121/C11CD76501  เครื่องพิมพ์แท็งค์แท้ (PR1-000610) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2990</v>
+        <v>120</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>2990</v>
+        <v>360</v>
       </c>
       <c r="H47" t="n">
         <v>-0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -5363,91 +5357,91 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>อั้น in คราม</t>
+          <t>ซายน์ ร้านบอยการยาง</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
+          <t>194/1 ม.1 ต.กองดิน</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>บางกะปิ/ Bang Kapi</t>
+          <t>แกลง</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>ระยอง</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
-          <t>660893549874</t>
+          <t>660884849453</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Prawit Saiyard</t>
+          <t>Phacharawan</t>
         </is>
       </c>
       <c r="Z47" t="n">
-        <v>2990</v>
+        <v>360</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>24 Dec 2023 17:42</t>
+          <t>25 Dec 2023 15:53</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
+          <t>194/1 ม.1 ต.กองดิน</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>800185367747863</t>
+          <t>795619003564701</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ME6-000875</t>
+          <t>PR5-000548</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
+          <t>CANON PIXMA G3010 ปริ้นเตอร์อิ๊งค์เจ็ต(PR5-000548) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>109</v>
+        <v>3450</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>218</v>
+        <v>3450</v>
       </c>
       <c r="H48" t="n">
         <v>-0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -5467,63 +5461,63 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>อานันท์  แก้วคำมา</t>
+          <t>สมปอง</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
+          <t>ร้านคัลเลอร์ปริ้น เซียร์รังสิตชั้น3 ห้องtc095</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>เถิน/ Thoen</t>
+          <t>ลำลูกกา</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>ลำปาง/ Lampang</t>
+          <t>ปทุมธานี</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>52160</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
-          <t>660818852780</t>
+          <t>660972456631</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Maemoksat</t>
+          <t>สมปอง</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>218</v>
+        <v>3450</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>24 Dec 2023 18:14</t>
+          <t>25 Dec 2023 15:28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
+          <t>ร้านคัลเลอร์ปริ้น เซียร์รังสิตชั้น3 ห้องtc095</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>800216973475656</t>
+          <t>795629265983475</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5541,17 +5535,17 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1103</v>
+        <v>279</v>
       </c>
       <c r="H49" t="n">
         <v>-0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -5571,52 +5565,51 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
+          <t>เอกธนัช​ แสงโมลา</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+          <t>79/318​ มบ.ศุภาลัย​วิลล์​(ซ.วิลล์​3)​ ม.3​ ซ.วัดส้มเกลี้ยง​ ต.ศาลากลาง</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>ปากเกร็ด/ Pak Kret</t>
+          <t>บางกรวย</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>นนทบุรี</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t xml:space="preserve">0125566004236
-</t>
+          <t>3350800159669</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>660936415666</t>
+          <t>660849054331</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>weerapat Nimanong</t>
+          <t>วริฐา แสงโมลา</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>1103</v>
+        <v>279</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>24 Dec 2023 19:44</t>
+          <t>25 Dec 2023 16:34</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -5625,42 +5618,42 @@
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+          <t>79/318​ มบ.ศุภาลัย​วิลล์​(ซ.วิลล์​3)​ ม.3​ ซ.วัดส้มเกลี้ยง​ ต.ศาลากลาง</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>800216973475656</t>
+          <t>795635436062762</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SP2-001755</t>
+          <t>MS2-000945</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CANON Ink CL-57 CO หมึกพิมพ์ (SP2-001755) SP2-001755</t>
+          <t>KINGSTON 128GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Red) MS2-000945</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>545</v>
+        <v>255</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>1103</v>
+        <v>255</v>
       </c>
       <c r="H50" t="n">
         <v>-0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -5680,96 +5673,91 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
+          <t>เกรียงศักดิ์ คงประเสริฐ</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+          <t>333/90 หมู่ที่1 ถ.สุขุมวิท ต.บางปูใหม่ อ.เมือง</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>ปากเกร็ด/ Pak Kret</t>
+          <t>เมืองสมุทรปราการ</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>นนทบุรี/ Nonthaburi</t>
+          <t>สมุทรปราการ</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>11120</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0125566004236
-</t>
-        </is>
-      </c>
+          <t>10280</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
-          <t>660936415666</t>
+          <t>660819165599</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>weerapat Nimanong</t>
+          <t>เกรียงศักดิ์ คงประเสริฐ</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>1103</v>
+        <v>255</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>24 Dec 2023 19:44</t>
+          <t>25 Dec 2023 16:26</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+          <t>333/90 หมู่ที่1 ถ.สุขุมวิท ต.บางปูใหม่ อ.เมือง</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>800260379788783</t>
+          <t>799858548970134</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ME6-000970</t>
+          <t>ME6-000914</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
+          <t>KINGSTON SD Canvas GO Plus 64GB 170/70MB/s ME6-000914</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="H51" t="n">
         <v>-0</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -5789,91 +5777,91 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Hytham Kaddurah</t>
+          <t>นายธนภัทร ผิวเงิน</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
+          <t>ร้านถ่ายรูปบ้านขาม 260 หมู่ 10 บ้านนาขาม ตำบลศรีชมภู</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>บางละมุง/ Bang Lamung</t>
+          <t>โซ่พิสัย</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>ชลบุรี/ Chonburi</t>
+          <t>บึงกาฬ</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>38170</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
-          <t>660969847039</t>
+          <t>660957038298</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Hytham</t>
+          <t>นายธนภัทร ผิวเงิน</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>24 Dec 2023 21:20</t>
+          <t>25 Dec 2023 07:51</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
+          <t>ร้านถ่ายรูปบ้านขาม 260 หมู่ 10 บ้านนาขาม ตำบลศรีชมภู</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>800264598105304</t>
+          <t>799929924712449</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>SP2-1713+SP2-1714+SP2-1715+SP2-1716</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+          <t>Epson หมึกแท้รุ่น T00V (003) Ink Bottle Set 4 สี (SP2-1713+SP2-1714+SP2-1715+SP2-1716)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>279</v>
+        <v>800</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>558</v>
+        <v>800</v>
       </c>
       <c r="H52" t="n">
         <v>-0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -5893,91 +5881,91 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>จุฑารัตน์ สุกกรี</t>
+          <t>Zaw Min Tun</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
+          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>เมืองชุมพร/ Mueang Chumphon</t>
+          <t>คลองเตย</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>ชุมพร/ Chumphon</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>86190</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
-          <t>660630609279</t>
+          <t>660829623134</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>จุฑารัตน์</t>
+          <t>JH Aung Aung</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>558</v>
+        <v>800</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>24 Dec 2023 21:35</t>
+          <t>24 Dec 2023 01:32</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
+          <t>Rhythm Sukhumvit 42, 5 Soi Sukhumvit 42, Phra Khanong Subdistrict 5/177 · คลองเตย/ Khlong Toei</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>800288100533275</t>
+          <t>799930194244423</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MS4-000931</t>
+          <t>ME6-000876</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SANDISK Extreme SDSSDE61 Portable SSD 1TB (Sky-Blue color) MS4-000931</t>
+          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2990</v>
+        <v>155</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>2990</v>
+        <v>155</v>
       </c>
       <c r="H53" t="n">
         <v>-0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -5997,47 +5985,47 @@
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>อนุชิต ไตรอรุณ</t>
+          <t>ภูษิต  ปาปะเก</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
+          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
-          <t>ลำลูกกา/ Lam Luk Ka</t>
+          <t>เมืองสมุทรปราการ</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>ปทุมธานี/ Pathum Thani</t>
+          <t>สมุทรปราการ</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>10280</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
-          <t>660865654708</t>
+          <t>660890528126</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>anuchit traiaroon</t>
+          <t>ภูษิต  ปาปะเก</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>2990</v>
+        <v>155</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>24 Dec 2023 22:02</t>
+          <t>24 Dec 2023 03:33</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
@@ -6046,42 +6034,42 @@
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
+          <t>390/210  หมู่บ้านทรัพย์นครบางปู  ต.บางปูใหม่   เมือง · บางปูใหม่/ Bang Pu Mai</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>800290334435407</t>
+          <t>799963152618334</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SP2-001753</t>
+          <t>ME6-000960</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+          <t>SanDisk Ultra microSDXC, SQUAB 64GB, A1, C10, U1, UHS-I, 140MB/s R, 4x6, 10Y</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="H54" t="n">
         <v>-0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -6101,91 +6089,95 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>กัญญ์ณณัฏฐ์ สุริยะฉาย</t>
+          <t>อังษณา พรมทัณ</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
+          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>บึงกุ่ม/ Bueng Kum</t>
+          <t>ดุสิต</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>กรุงเทพมหานคร</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>10240</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1103700155899</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>660806315727</t>
+          <t>660898881040</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Kannanat Suriyachai</t>
+          <t>อังษณา พรมทัณ</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>24 Dec 2023 22:24</t>
+          <t>24 Dec 2023 07:45</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
+          <t>ถนนประดิพัทธิ บ้านพักกรมช่างอากาศ บางซื่อ 1/552 อาคาร B2 ห้อง 1504</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>800302183049682</t>
+          <t>799969900750744</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PR5-000582</t>
+          <t>MS2-000944</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+          <t>KINGSTON 64GB USB3.2 Gen 1 DataTraveler Exodia M (Black + Blue) MS2-000944</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1860</v>
+        <v>135</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1860</v>
+        <v>135</v>
       </c>
       <c r="H55" t="n">
         <v>-0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -6205,91 +6197,91 @@
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>รพีพงศ์ ศศิธรวัณณ์</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1/174 Lalisa Moo9 Thawangtan</t>
+          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>สารภี/ Saraphi</t>
+          <t>เมืองนนทบุรี</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>เชียงใหม่/ Chiang Mai</t>
+          <t>นนทบุรี</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>50140</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
-          <t>660932824520</t>
+          <t>660982523524</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Reaw</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>1860</v>
+        <v>135</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>24 Dec 2023 23:30</t>
+          <t>24 Dec 2023 07:46</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>1/174 Lalisa Moo9 Thawangtan</t>
+          <t>78/42 หมู่ 6 ซ.ประชาราษฎร์5แยก1 ต.ตลาดขวัญ อ.เมือง จ.นนทบุรี 11000</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>800308146152775</t>
+          <t>799979507148952</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MS2-000845</t>
+          <t>IP7-001199</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SANDISK USB2.0 Cruzer Blade 32GB MS2-000845</t>
+          <t>LOGITECH COMBO TOUCH FOR iPAD 10th GENERATION (1Y) IP7-001199 (จำนวนจำกัด)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>115</v>
+        <v>3790</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>115</v>
+        <v>3790</v>
       </c>
       <c r="H56" t="n">
         <v>-0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -6309,91 +6301,91 @@
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>ปิยวัจณ์ ยศเมฆ</t>
+          <t>HADIN</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>43/2 ม.3 ต.เลม็ด อ.ไชยา จ.สุราษฎร์ธานี</t>
+          <t>198/4, Moo 10</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr">
         <is>
-          <t>ไชยา/ Chaiya</t>
+          <t>หางดง</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>สุราษฎร์ธานี/ Surat Thani</t>
+          <t>เชียงใหม่</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>84110</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
-          <t>660902138035</t>
+          <t>660828210693</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Piyawat Yotmet</t>
+          <t>Mehdi Hadim</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>115</v>
+        <v>3790</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>24 Dec 2023 23:37</t>
+          <t>24 Dec 2023 08:21</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>43/2 ม.3 ต.เลม็ด อ.ไชยา จ.สุราษฎร์ธานี</t>
+          <t>198/4, Moo 10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>800321509632607</t>
+          <t>800009590366429</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MNL-001916</t>
+          <t>SP4-000302</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
+          <t>EPSON RB S015639/LQ-310 ตลับผ้าหมึก SP4-000302</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6990</v>
+        <v>120</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>6990</v>
+        <v>240</v>
       </c>
       <c r="H57" t="n">
         <v>-0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -6413,91 +6405,95 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>ขวัญชัย ศิริสุข</t>
+          <t>มลฤดี  รู้รักตน</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>หมู่ 6 ท่าตูม 173/2</t>
+          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr">
         <is>
-          <t>ศรีมหาโพธิ/ Si Maha Phot</t>
+          <t>ปากเกร็ด</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>ปราจีนบุรี/ Prachin Buri</t>
+          <t>นนทบุรี</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>25140</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr"/>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>0125537003979</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>660863245964</t>
+          <t>660899910145</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Khwanchai Sirisuk</t>
+          <t>Monludee Rurakton</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>6990</v>
+        <v>240</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>25 Dec 2023 00:09</t>
+          <t>24 Dec 2023 10:12</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>หมู่ 6 ท่าตูม 173/2</t>
+          <t>43/26-27  หมู่8 ถนนติวานนท์</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>800350722394774</t>
+          <t>800045958990703</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MS4-000826</t>
+          <t>MNL-001862</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SANDISK Extreme SDSSDE61 Portable SSD 2TB MS4-000826</t>
+          <t>ACER LED Monitor EH200Qbi - 19.5"/TN/75Hz/3Y/MNL-001862</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4990</v>
+        <v>1890</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>4990</v>
+        <v>1890</v>
       </c>
       <c r="H58" t="n">
         <v>-0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -6517,91 +6513,91 @@
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>นวัช ทัฬหิกรณ์</t>
+          <t>นายคณกฤช มัชฌิมา</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>55 อาคาร เอ.เอ.แคปปิตอลรัชดา ถ.รัชดาภิเษก ชั้น7</t>
+          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>ดินแดง/ Din Daeng</t>
+          <t>เมืองพิจิตร</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>กรุงเทพมหานคร/ Bangkok</t>
+          <t>พิจิตร</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>66000</t>
         </is>
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
-          <t>660801491424</t>
+          <t>66899594344</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>ntunhikorn</t>
+          <t>นายคณกฤช  มัชฌิมา</t>
         </is>
       </c>
       <c r="Z58" t="n">
-        <v>4990</v>
+        <v>1890</v>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>25 Dec 2023 02:05</t>
+          <t>24 Dec 2023 11:35</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>55 อาคาร เอ.เอ.แคปปิตอลรัชดา ถ.รัชดาภิเษก ชั้น7</t>
+          <t>สำนักงานข่าว ททบ.5พิจิตร เลขที่ 2/218 ถ.ศรีมาลา อ.เมือง จ.พิจิตร</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>800397746150140</t>
+          <t>800074729069035</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GMA-001466</t>
+          <t>PR5-000610</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LOGA GAMING SWITCH MECHANICAL SWITCHES : NOMYEN LINEAR 35 PCS (GMA-001466)</t>
+          <t>EPSON Printer L3210 STD/C11CJ68501 (PR5-000610) (จำกัดการซื้อ1ออเดอร์ไม่เกิน3เครื่อง) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>390</v>
+        <v>3730</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>390</v>
+        <v>3730</v>
       </c>
       <c r="H59" t="n">
         <v>-0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>packed</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -6621,47 +6617,51 @@
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>ปรเมศร์ ป้องไฝ</t>
+          <t>เฉลิม พรพงษ์</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>หอพักรุ่งแสงทอง 97 ,หมูู่10 ,ถนนพหลโยธิน หอพักรุ้งแสงทอง อาคารA ชั้น3 · ทรายขาว/ Sai Khao</t>
+          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr">
         <is>
-          <t>พาน/ Phan</t>
+          <t>ธัญบุรี</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>เชียงราย/ Chiang Rai</t>
+          <t>ปทุมธานี</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>57120</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr"/>
+          <t>12130</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>1195703950</t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>660821609308</t>
+          <t>660838464600</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>ปรเมศร์ ป้องไฝ</t>
+          <t>Chaloem Phornphong</t>
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>390</v>
+        <v>3730</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>25 Dec 2023 08:14</t>
+          <t>24 Dec 2023 12:43</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
@@ -6670,46 +6670,42 @@
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>หอพักรุ่งแสงทอง 97 ,หมูู่10 ,ถนนพหลโยธิน หอพักรุ้งแสงทอง อาคารA ชั้น3 · ทรายขาว/ Sai Khao</t>
+          <t>69/330 ม.3 ซ.4/1 หมู่บ้านฟ้ารังสิตคลอง4 ถ.รังสิต-นครนายก ต.บึงยี่โถ อ.ธัญบุรี จ.ปทุมธานี 12130. · บึงยี่โถ/ Bueng Yitho</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>800420111896380</t>
+          <t>800085587433269</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GMP-000142</t>
+          <t>PR5-000582</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>RAZER MOUSE PAD GOLIATHUS CHROMA EXTENDED GMP-000142</t>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2190</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Color Family:Black</t>
-        </is>
-      </c>
+        <v>1860</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>2190</v>
+        <v>1860</v>
       </c>
       <c r="H60" t="n">
         <v>-0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>ready_to_ship</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -6729,60 +6725,3426 @@
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Sun Shenghuai</t>
+          <t>สมภพ บูรณพิมพ์</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Room 132, BFC 1, 187/3 บางวัว 4 Bang Wua, Bang Pakong District, Chachoengsao 24180  132</t>
+          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr">
         <is>
-          <t>บางปะกง/ Bang Pakong</t>
+          <t>บ้านบึง</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>ฉะเชิงเทรา/ Chachoengsao</t>
+          <t>ชลบุรี</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>24130</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>0-993-0004-6770-1</t>
-        </is>
-      </c>
+          <t>20220</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr">
         <is>
-          <t>660909087666</t>
+          <t>660894014557</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>909087666</t>
+          <t>*******874</t>
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>2190</v>
+        <v>1860</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>25 Dec 2023 08:59</t>
+          <t>24 Dec 2023 13:30</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>ถ. หนองชาก-เนินโมก/โรงน้ำสิงห์ทอง 99/4 ม.1ต.หนองอิรุณอ.บ้านบึงจ.ชลบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>800090726148364</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MS2-000844</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SANDISK USB2.0 Cruzer Blade 16GB MS2-000844</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>115</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>115</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>นาย จิรวัฒน์ อ่อนคล้าย</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>ตาคลี</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>นครสวรรค์</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>660814081091</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>0814081091</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>115</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 13:23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>60 หมู่12 หมู่บ้านเขาดิน ซอยบ้านเหนือ2 · ตาคลี/ Takhli</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>800094782668343</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PR5-000503</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CANON PIXMA E-410 Black</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Color Family:Black</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1335</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ready_to_ship</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Ethel Joy</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>บางบัวทอง</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>11110</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>660832393046</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Ethel Joy</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>1335</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 13:51</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>30</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>138/68 CondoBangyai Square B2, Moo 12,  3 · บางรักพัฒนา/ Bang Rak Phatthana</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>800122510696050</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SP2-001753</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>279</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>279</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>ศิริกัญญา​ โต​เจริญ​</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>12ม.6ต.บางแก้ว</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>เมืองฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>24000</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>660819831278</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>ศิริกัญญา โตเจริญ</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>279</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 14:40</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
         <v>38</v>
       </c>
-      <c r="AD60" t="inlineStr">
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>12ม.6ต.บางแก้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>800152733254698</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PR5-000573</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HP Smart Tank 515 AiO Printer / 1TJ09A (2Y*) (PR5-000573) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3490</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ready_to_ship</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>สว่างวรรณ บุตรนาค</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>เมืองนนทบุรี</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>3120100492162</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>660891116186</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>สว่างวรรณ บุตรนาค</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>3490</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 16:16</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>42/216 ซ.เลี่ยงเมืองนนทบุรี10 ต.บางกระสอ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>800173538628211</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>680</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>680</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>สมาน  สบตุ๋ย</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>บางนา</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>10260</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>660878176408</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>สมาน</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>680</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 17:21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>98/226 ม.รุ่งเรื่อง ซ.6 ถ.สรรพาวุธ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>800178151179981</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>PR1-000610</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>EPSON Printer L121/C11CD76501  เครื่องพิมพ์แท็งค์แท้ (PR1-000610) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2990</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2990</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ready_to_ship</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>อั้น in คราม</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>บางกะปิ</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>660893549874</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Prawit Saiyard</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>2990</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 17:42</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1  แขวงคลองจั่น  บ้านเลขที่ 83 ซอยลาดพร้าว 107 แยก 1 , แขวงคลองจั่น · คลองจั่น</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>800185367747863</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ME6-000875</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>109</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>218</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>อานันท์  แก้วคำมา</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>เถิน</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>52160</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>660818852780</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Maemoksat</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>218</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 18:14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>ร้านแม่มอกดาวเทียม  116 หมู่ 3 ต.แม่มอก</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>800216973475656</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SP2-001753</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>279</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>ปากเกร็ด</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0125566004236
+</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>660936415666</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>weerapat Nimanong</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>1103</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 19:44</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>800216973475656</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SP2-001755</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CANON Ink CL-57 CO หมึกพิมพ์ (SP2-001755) SP2-001755</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>545</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>บริษัท สิบล้านทรัพย์ จำกัด</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>ปากเกร็ด</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>11120</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0125566004236
+</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>660936415666</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>weerapat Nimanong</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>1103</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 19:44</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>102/157 ถ.ติวานนท์ ม.8 ม.รุ่งเรืองธานี ต.บางพูด</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>800260379788783</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>ME6-000970</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SanDisk Extreme SDXC, SDXV2 64GB, V30, U3, C10, UHS-I, 170MB/s R, 80MB/s W, 4x6, Lifetime Limited</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>299</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>299</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ready_to_ship</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Hytham Kaddurah</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>บางละมุง</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>20150</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>660969847039</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Hytham</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>299</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 21:20</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Dusit Pattaya Park 118/77 Moo 11  Soi Watyansangwararam,Huai Yai,  · ห้วยใหญ่/ Huai Yai</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>800264598105304</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SP2-001753</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>279</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>558</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>จุฑารัตน์ สุกกรี</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>เมืองชุมพร</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>ชุมพร</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>86190</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>660630609279</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>จุฑารัตน์</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>558</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 21:35</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>ท่าไม้ลาย3 130ม.5 ต.วังใหม่</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>800288100533275</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MS4-000931</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SANDISK Extreme SDSSDE61 Portable SSD 1TB (Sky-Blue color) MS4-000931</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2990</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2990</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>อนุชิต ไตรอรุณ</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>ลำลูกกา</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>ปทุมธานี</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>12150</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>660865654708</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>anuchit traiaroon</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>2990</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 22:02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>69/103 บ้านฟ้าปิยรมย์เฟส 3 หมู่ 5 ตำบลบึงคำพร้อย</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>800290334435407</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SP2-001753</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CANON Ink PG-47 BK (SP2-001753) หมึกพิมพ์ SP2-001753</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>279</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="n">
+        <v>279</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>กัญญ์ณณัฏฐ์ สุริยะฉาย</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>บึงกุ่ม</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>660806315727</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Kannanat Suriyachai</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>279</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 22:24</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>28/186 หมู่บ้านโกลเด้นทาวน์1 ซอยนวมินทร์42 แยก 27 ถนนนวมินทร์ แขวงคลองกุ่ม0806315727</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>800302183049682</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PR5-000582</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CANON PIXMA E3370 (1Y) (PR5-000582) พร้อมหมึกแท้ในกล่อง 1 ชุด</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1860</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ready_to_ship</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1/174 Lalisa Moo9 Thawangtan</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>สารภี</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>50140</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>660932824520</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Jane</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>1860</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 23:30</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>1/174 Lalisa Moo9 Thawangtan</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>800308146152775</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MS2-000845</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SANDISK USB2.0 Cruzer Blade 32GB MS2-000845</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>115</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>115</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>ปิยวัจณ์ ยศเมฆ</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>43/2 ม.3 ต.เลม็ด อ.ไชยา จ.สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>ไชยา</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>84110</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>660902138035</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Piyawat Yotmet</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>24 Dec 2023 23:37</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>43/2 ม.3 ต.เลม็ด อ.ไชยา จ.สุราษฎร์ธานี</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>800321509632607</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MNL-001916</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>6990</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6990</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ready_to_ship</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>ขวัญชัย ศิริสุข</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>หมู่ 6 ท่าตูม 173/2</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>ศรีมหาโพธิ</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>ปราจีนบุรี</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>25140</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>660863245964</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Khwanchai Sirisuk</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>6990</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 00:09</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>หมู่ 6 ท่าตูม 173/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>800350722394774</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MS4-000826</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SANDISK Extreme SDSSDE61 Portable SSD 2TB MS4-000826</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>4990</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4990</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>นวัช ทัฬหิกรณ์</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>55 อาคาร เอ.เอ.แคปปิตอลรัชดา ถ.รัชดาภิเษก ชั้น7</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>ดินแดง</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>660801491424</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>ntunhikorn</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>4990</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 02:05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>55 อาคาร เอ.เอ.แคปปิตอลรัชดา ถ.รัชดาภิเษก ชั้น7</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>800397746150140</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GMA-001466</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LOGA GAMING SWITCH MECHANICAL SWITCHES : NOMYEN LINEAR 35 PCS (GMA-001466)</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>390</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>390</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>packed</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>ปรเมศร์ ป้องไฝ</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>หอพักรุ่งแสงทอง 97 ,หมูู่10 ,ถนนพหลโยธิน หอพักรุ้งแสงทอง อาคารA ชั้น3 · ทรายขาว/ Sai Khao</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>พาน</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>เชียงราย</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>57120</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>660821609308</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>ปรเมศร์ ป้องไฝ</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>390</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 08:14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>หอพักรุ่งแสงทอง 97 ,หมูู่10 ,ถนนพหลโยธิน หอพักรุ้งแสงทอง อาคารA ชั้น3 · ทรายขาว/ Sai Khao</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>800420111896380</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GMP-000142</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>RAZER MOUSE PAD GOLIATHUS CHROMA EXTENDED GMP-000142</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2190</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Color Family:Black</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>2190</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Sun Shenghuai</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
         <is>
           <t>Room 132, BFC 1, 187/3 บางวัว 4 Bang Wua, Bang Pakong District, Chachoengsao 24180  132</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>บางปะกง</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>ฉะเชิงเทรา</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>24130</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>0-993-0004-6770-1</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>660909087666</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>909087666</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>2190</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 08:59</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Room 132, BFC 1, 187/3 บางวัว 4 Bang Wua, Bang Pakong District, Chachoengsao 24180  132</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>800459180604025</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SP2-1753+SP2-1755</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CANON Ink PG-47 BK + CL-57 CO (ชุด 2 สี) หมึกพิมพ์ SP2-1753+SP2-1755</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>824</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>824</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>ครูผักกาด</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>โรงเรียนบ้านห้วยไคร้ หมู่ 6  ตำบลโนนปอแดง</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>ผาขาว</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>เลย</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>42240</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>660933296250</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>พรทิพย์ บุญมา</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>824</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 10:40</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>โรงเรียนบ้านห้วยไคร้ หมู่ 6  ตำบลโนนปอแดง</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>800460919914737</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>ME6-000876</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>KINGSTON MicroSDXC Canvas Select Plus 100R 64GB, 100/85MB/s ME6-000876</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>155</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>310</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>ปัทมา โอสถานนท์</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>81/10 ซอยรามคำแหง 195/1 ถนนรามคำแหง แขวงมีนบุรี</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>มีนบุรี</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>10510</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>660866682488</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Osathanon Lekja</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>310</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 10:28</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>81/10 ซอยรามคำแหง 195/1 ถนนรามคำแหง แขวงมีนบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>800470589262801</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>680</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1360</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>จ.ส.อ.เจษฎา แสงสว่าง</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>110 หมู่7 ต.โพธิ์สัย</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>ศรีสมเด็จ</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>45280</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>660956538690</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>เจษฎา แสงว่าง</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>1360</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 11:14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>110 หมู่7 ต.โพธิ์สัย</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>800479784216703</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>680</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>680</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>มงคล  พรมแก้ว</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>94 หมู่ 4 ต. รันบุรี</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>รัตนบุรี</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>สุรินทร์</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>32130</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>660914484945</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>มงคล  พรมแก้ว</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>680</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 11:23</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>94 หมู่ 4 ต. รันบุรี</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>800539916451131</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MS2-000820</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SANDISK USB2.0 Cruzer Blade CZ50 32GB/BL MS2-000820</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>115</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>รัชพงษ์ บุญจันทร์</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>41หมู่2 ต เชียงม่วน</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>เชียงม่วน</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>56160</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>3199900370451</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>660884629438</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>รัชพงษ์  บุญจันทร์</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 14:49</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>41หมู่2 ต เชียงม่วน</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>800539916451131</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MS2-000845</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SANDISK USB2.0 Cruzer Blade 32GB MS2-000845</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>115</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>รัชพงษ์ บุญจันทร์</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>41หมู่2 ต เชียงม่วน</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>เชียงม่วน</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>พะเยา</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>56160</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>3199900370451</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>660884629438</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>รัชพงษ์  บุญจันทร์</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>1150</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 14:49</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>41หมู่2 ต เชียงม่วน</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>800543310693991</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>680</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>680</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Alisa</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>บริษัท อูดาชี จำกัด 898/97 ถ.ประเสริฐมนูกิจ · คลองกุ่ม/ Khlong Kum</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>บึงกุ่ม</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>10240</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>0105556028914</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>660979987888</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>680</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 13:09</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>บริษัท อูดาชี จำกัด 898/97 ถ.ประเสริฐมนูกิจ · คลองกุ่ม/ Khlong Kum</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>800561589380868</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MMH-002881</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>REALME Buds T300 Youth White (MMH-002881)</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1199</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1199</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Unpaid</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>kenji kusno</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Lumpini Ville Sukhumvit 76-Bearing Station 1, Sukhumvit 76, Samrong Nuea. TOWER C, C719 762/164 · สำโรงเหนือ/ Samrong Nuea</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>เมืองสมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>10270</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>660611470134</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>kenji k</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>1199</v>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 14:08</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>Lumpini Ville Sukhumvit 76-Bearing Station 1, Sukhumvit 76, Samrong Nuea. TOWER C, C719 762/164 · สำโรงเหนือ/ Samrong Nuea</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>800583330495900</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ME6-000875</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>KINGSTON MicroSDHC Canvas Select Plus 100R 32GB, 100/85MB/s ME6-000875</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>109</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>109</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>ชฎาภรณ์ บุญภา</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>86 หมู่​ 2 ตำบล ป่าตัน 4แยกหน้าวัดบ.ปงแยกไปบ.นากว้าวติดร้านซ่อมรถ</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>แม่ทะ</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>ลำปาง</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>52150</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>660926817236</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>ชฎาภรณ์ บุญภา</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>109</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 14:30</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>86 หมู่​ 2 ตำบล ป่าตัน 4แยกหน้าวัดบ.ปงแยกไปบ.นากว้าวติดร้านซ่อมรถ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>800608901205236</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BROTHER INK Cartridge BT-D60BK+BT-5000 C+M+Y SP2-1703+SP2-1596+SP2-1597+SP2-1598</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>680</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="n">
+        <v>680</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>ดวงสมร  ฤทธิรงค์</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>4  ซอยรัตนาธิเบร์ 8  แยก 1/1 ถนนรัตนาธิเบศร์ ตำบลบางกระส</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>เมืองนนทบุรี</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>นนทบุรี</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>0123561004368</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>660899268651</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>ดวงสมร ฤทธิรงค์</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>680</v>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 15:13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>4  ซอยรัตนาธิเบร์ 8  แยก 1/1 ถนนรัตนาธิเบศร์ ตำบลบางกระส</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>800615788930766</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MS6-000169</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>WD BLACK SN770 500GB M.2 2280 NVMe Gen4 (WDS500G3X0E) (5Y) MS6-000169</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1390</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>ปรีชา ศิริวรกุลชัย</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>17/11 ถ.เพลินจิต</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>เมืองร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>ร้อยเอ็ด</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>660850068584</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Preecha siri</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>1390</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 16:04</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>17/11 ถ.เพลินจิต</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>800626196655490</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MNL-001916</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>จอมอนิเตอร์ HP 2K Gaming Monitor X32 - 31.5"/IPS/165Hz/3Y*3 / MNL-001916</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>6990</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>6990</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Alexander Klauzer</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>VIP Condo Chain, 137/107, M.3 Sukhumvit Rd., Na Jomtien</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>สัตหีบ</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>ชลบุรี</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>20180</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>660873280505</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Alexander Klauzer</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>6990</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 16:18</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="n">
+        <v>125</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>VIP Condo Chain, 137/107, M.3 Sukhumvit Rd., Na Jomtien</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>800638908775211</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MS6-000164</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>WD BLUE SN570 250GB SSD NVMe M.2 2280 (WDS250G3B0C) (5Y) MS6-000164</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>590</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>590</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>สำนักงานใหญ่</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>คมสันต์ บุญเรือน</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>423/58 ซ.จรัญสนิทวงศ์ 35แยก7 หลังศิรินภาแมนชั่น แขวง บางขุนศรี</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>บางกอกน้อย</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>กรุงเทพมหานคร</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>10700</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>660655867977</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>แจ็คคุง ได้เพ</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>590</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>25 Dec 2023 16:14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>423/58 ซ.จรัญสนิทวงศ์ 35แยก7 หลังศิรินภาแมนชั่น แขวง บางขุนศรี</t>
         </is>
       </c>
     </row>

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -841,7 +841,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O77" t="inlineStr"/>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O79" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O80" t="inlineStr"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O83" t="inlineStr"/>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O84" t="inlineStr"/>
@@ -9486,7 +9486,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O86" t="inlineStr"/>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O88" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O90" t="inlineStr"/>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O92" t="inlineStr"/>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O94" t="inlineStr"/>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O96" t="inlineStr"/>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O97" t="inlineStr"/>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O98" t="inlineStr"/>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O99" t="inlineStr"/>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O102" t="inlineStr"/>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O103" t="inlineStr"/>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O105" t="inlineStr"/>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O107" t="inlineStr"/>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O108" t="inlineStr"/>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O109" t="inlineStr"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O110" t="inlineStr"/>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O111" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O113" t="inlineStr"/>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O115" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O118" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O119" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O120" t="inlineStr"/>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O121" t="inlineStr"/>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O122" t="inlineStr"/>
@@ -13630,7 +13630,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O124" t="inlineStr"/>
@@ -13962,7 +13962,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O127" t="inlineStr"/>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O128" t="inlineStr"/>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O130" t="inlineStr"/>
@@ -14386,7 +14386,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O131" t="inlineStr"/>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O132" t="inlineStr"/>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O133" t="inlineStr"/>
@@ -14814,7 +14814,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O135" t="inlineStr"/>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O140" t="inlineStr"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O141" t="inlineStr"/>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O143" t="inlineStr"/>
@@ -16018,7 +16018,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O146" t="inlineStr"/>
@@ -16122,7 +16122,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>สำนักงานใหญ่</t>
+          <t>สาขาย่อย</t>
         </is>
       </c>
       <c r="O147" t="inlineStr"/>

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -761,7 +761,8 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>603565000061.0</t>
+          <t xml:space="preserve">0603565000061
+</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -981,7 +982,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1027243678.0</t>
+          <t>1027243678</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>653554001168.0</t>
+          <t>0653554001168</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1413,7 +1414,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3901000219646.0</t>
+          <t>3901000219646</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2153,7 +2154,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>3600700003397.0</t>
+          <t>3600700003397</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2265,7 +2266,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1100400631595.0</t>
+          <t>1100400631595</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -1619,7 +1619,11 @@
           <t>60/9 หมู่บ้านแคทลียา ซ.หทัยราษฎร์37 ถ.หทัยราษฎร์ แขวงคลองสามวาตะวันตก</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>สามวาตะวันตก</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>คลองสามวา</t>
@@ -2087,7 +2091,11 @@
           <t>72/219 หมู่ 11 ( ม.กลาโหม ) ต.ไร่ขิง</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>ไร่ขิง</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>สามพราน</t>
@@ -2433,7 +2441,11 @@
           <t>183 ม.7 ต.ทัพหลวง อ.หนองหญ้าไซ</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ทัพหลวง</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
           <t>หนองหญ้าไซ</t>
@@ -2547,7 +2559,11 @@
           <t>128 ม.1 ต.บ่อภาค</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>บ่อภาค</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
           <t>ชาติตระการ</t>
@@ -3259,7 +3275,11 @@
           <t>วัดวรจรรยาวาส   ถ.เจริญกรุง ซอย 72  แขวงวัดพระยาไกร</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>วัดพระยาไกร</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
           <t>บางคอแหลม</t>
@@ -3373,7 +3393,11 @@
           <t>109/176 หมู่บ้านชวนชื่นโมดัส แจ้งวัฒนะ ซ.สหกรณ์3 ถ.เลี่ยงเมืองปากเกร็ด ต.บางพูด</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>บางพูด</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
           <t>ปากเกร็ด</t>
@@ -4093,7 +4117,11 @@
           <t>328/3 ถ. ลาดหญ้า, แขวงคลองสาน, เขตคลองสาน</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>คลองสาน</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
           <t>คลองสาน</t>
@@ -4443,7 +4471,11 @@
           <t>88/19 ซอยเอกเจริญ8 หมู่บ้านเมืองเอกโครงการ6 ต.หลักหก อ.เมือง จ.ปทุมธาน</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>หลักหก</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
           <t>เมืองปทุมธานี</t>
@@ -4557,7 +4589,11 @@
           <t>88/19 ซอยเอกเจริญ8 หมู่บ้านเมืองเอกโครงการ6 ต.หลักหก อ.เมือง จ.ปทุมธาน</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>หลักหก</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>เมืองปทุมธานี</t>
@@ -5029,7 +5065,11 @@
           <t>144/1 (บ้านคำวัน)บ.ธาตุนาเวง  ต.ธาตุเชิงชุม อ.เมือง จ.สกลนคร 47000</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>ธาตุเชิงชุม</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
           <t>เมืองสกลนคร</t>
@@ -5379,7 +5419,11 @@
           <t>38/4 หมู่ 5 ห้อง418 ถนนเลียบคลองระพีพัฒน์ ต.พยอม</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>พยอม</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr">
         <is>
           <t>วังน้อย</t>
@@ -5611,7 +5655,11 @@
           <t>คลังน้ำมัน​ IRPC​ พระประแดง​ 169 ม.9 ต.บางครุ อ.พระประแดง จ.สมุทรปราการ</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>บางครุ</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
           <t>พระประแดง</t>
@@ -5842,7 +5890,11 @@
           <t>บริษัท พี เอส เมนแลนด์ จำกัด (สำนักงานใหญ่) 58 หมู่ 9 ตำบลคลองสอง -</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>คลองสอง</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
           <t>คลองหลวง</t>
@@ -5960,7 +6012,11 @@
           <t>สาขาที่ 00001 เลขที่ 15/22 ม.5 ต.นาตาขวัญ</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>นาตาขวัญ</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
           <t>เมืองระยอง</t>
@@ -6082,7 +6138,11 @@
           <t>สาขาที่ 00001 เลขที่ 15/22 ม.5 ต.นาตาขวัญ</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>นาตาขวัญ</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr">
         <is>
           <t>เมืองระยอง</t>
@@ -6208,7 +6268,11 @@
           <t>94/3ม.3 ต.บางบุตร อ.บ้านค่าย จ.ระยอง 21120</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>บางบุตร</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
           <t>บ้านค่าย</t>
@@ -6920,7 +6984,11 @@
           <t>134/2 บ้านหลังคาสีเทาตรงข้ามแท้งน้ำสูง หมู่4 ถ.หนองบัว ด่านสิงขร หลักกม.2 ต.เกาะหลัก</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>เกาะหลัก</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
           <t>เมืองประจวบคีรีขันธ์</t>
@@ -7262,7 +7330,11 @@
           <t>74/4 หมู่4 ตำบลทัพหลวง</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>ทัพหลวง</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr">
         <is>
           <t>เมืองนครปฐม</t>
@@ -8324,7 +8396,11 @@
           <t>235 ม.6 ซอยเพชรเกษม 126/1 ต.อ้อมน้อย อ.กระทุ่มแบน จ.สมุทรสาคร 74130</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>อ้อมน้อย</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr">
         <is>
           <t>กระทุ่มแบน</t>
@@ -8556,7 +8632,11 @@
           <t>10/2 ม.7 ต.ทะเลทรัพย์</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>ทะเลทรัพย์</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr">
         <is>
           <t>ปะทิว</t>
@@ -8792,7 +8872,11 @@
           <t>หจก.โรงโม่หินศิลาโชคชัย 40 หมู่ 3 ต.หนองหัวแรต</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>หนองหัวแรต</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr">
         <is>
           <t>หนองบุญมาก</t>
@@ -9386,7 +9470,11 @@
           <t>81หมู่1ต.คลองวาฬ อ.เมือง</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>คลองวาฬ</t>
+        </is>
+      </c>
       <c r="V76" t="inlineStr">
         <is>
           <t>เมืองประจวบคีรีขันธ์</t>
@@ -9622,7 +9710,11 @@
           <t>104 หมู่ 7  ต. ท่าข้าม  (ลานไม้)</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>ท่าข้าม</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr">
         <is>
           <t>หาดใหญ่</t>
@@ -10094,7 +10186,11 @@
           <t>98/180 หมู่บ้านพลีโน่ สุขุมวิท-บางนา ถนนบางนา-ตราด ซอยโรงเรียนราชวินิตบางแก้ว ต.บางแก้ว -</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>บางแก้ว</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr">
         <is>
           <t>บางพลี</t>
@@ -10330,7 +10426,11 @@
           <t>บริษัท พี เอส เมนแลนด์ จำกัด (สำนักงานใหญ่) 58 หมู่ 9 ตำบลคลองสอง -</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>คลองสอง</t>
+        </is>
+      </c>
       <c r="V84" t="inlineStr">
         <is>
           <t>คลองหลวง</t>
@@ -10448,7 +10548,11 @@
           <t>7/1 หมู่1 ต. กุดน้ำใส อ. น้ำพอง จ.ขอนแก่</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>กุดน้ำใส</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr">
         <is>
           <t>น้ำพอง</t>
@@ -10688,7 +10792,11 @@
           <t>เลขที่ 16 ซอย เฉลิมพระเกียรติ ร.9 ซอย 71  ถนนเฉลิมพระเกียรติ ร.9 , ดอกไม้, ประเวศ</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>ดอกไม้</t>
+        </is>
+      </c>
       <c r="V87" t="inlineStr">
         <is>
           <t>ประเวศ</t>

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -1645,7 +1645,7 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>58 หมู่ 9 -</t>
+          <t>58 หมู่ 9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>98/180 หมู่บ้านพลีโน่ สุขุมวิท-บางนา ถนนบางนา-ตราด ซอยโรงเรียนราชวินิตบางแก้ว -</t>
+          <t>98/180 หมู่บ้านพลีโน่ สุขุมวิท-บางนา ถนนบางนา-ตราด ซอยโรงเรียนราชวินิตบางแก้ว</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>58 หมู่ 9 -</t>
+          <t>58 หมู่ 9</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -687,10 +691,8 @@
       <c r="Z2" t="n">
         <v>3265</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2026-04-16 00:36</t>
-        </is>
+      <c r="AA2" s="2" t="n">
+        <v>46128.025</v>
       </c>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
@@ -805,10 +807,8 @@
       <c r="Z3" t="n">
         <v>5302.5</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-04-16 07:02</t>
-        </is>
+      <c r="AA3" s="2" t="n">
+        <v>46128.29305555556</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
@@ -923,10 +923,8 @@
       <c r="Z4" t="n">
         <v>5088.75</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-04-16 07:49</t>
-        </is>
+      <c r="AA4" s="2" t="n">
+        <v>46128.32569444444</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
@@ -1049,10 +1047,8 @@
       <c r="Z5" t="n">
         <v>4620</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-04-16 09:29</t>
-        </is>
+      <c r="AA5" s="2" t="n">
+        <v>46128.39513888889</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
@@ -1167,10 +1163,8 @@
       <c r="Z6" t="n">
         <v>6427</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2026-04-16 10:11</t>
-        </is>
+      <c r="AA6" s="2" t="n">
+        <v>46128.42430555556</v>
       </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
@@ -1285,10 +1279,8 @@
       <c r="Z7" t="n">
         <v>1399</v>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2026-04-16 10:42</t>
-        </is>
+      <c r="AA7" s="2" t="n">
+        <v>46128.44583333333</v>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
@@ -1407,10 +1399,8 @@
       <c r="Z8" t="n">
         <v>6087.75</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:48</t>
-        </is>
+      <c r="AA8" s="2" t="n">
+        <v>46128.575</v>
       </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
@@ -1533,10 +1523,8 @@
       <c r="Z9" t="n">
         <v>4350.5</v>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-04-16 21:17</t>
-        </is>
+      <c r="AA9" s="2" t="n">
+        <v>46128.88680555556</v>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
@@ -1651,10 +1639,8 @@
       <c r="Z10" t="n">
         <v>1075.5</v>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-04-16 22:34</t>
-        </is>
+      <c r="AA10" s="2" t="n">
+        <v>46128.94027777778</v>
       </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
@@ -1773,10 +1759,8 @@
       <c r="Z11" t="n">
         <v>1188</v>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:48</t>
-        </is>
+      <c r="AA11" s="2" t="n">
+        <v>46129.36666666667</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
@@ -1895,10 +1879,8 @@
       <c r="Z12" t="n">
         <v>1188</v>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:45</t>
-        </is>
+      <c r="AA12" s="2" t="n">
+        <v>46129.36458333334</v>
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
@@ -2017,10 +1999,8 @@
       <c r="Z13" t="n">
         <v>896.03</v>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:48</t>
-        </is>
+      <c r="AA13" s="2" t="n">
+        <v>46129.49166666667</v>
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
@@ -2135,10 +2115,8 @@
       <c r="Z14" t="n">
         <v>1850.25</v>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-04-17 12:51</t>
-        </is>
+      <c r="AA14" s="2" t="n">
+        <v>46129.53541666667</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
@@ -2253,10 +2231,8 @@
       <c r="Z15" t="n">
         <v>1850.25</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-04-17 12:51</t>
-        </is>
+      <c r="AA15" s="2" t="n">
+        <v>46129.53541666667</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
@@ -2375,10 +2351,8 @@
       <c r="Z16" t="n">
         <v>756.6</v>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2026-04-17 14:45</t>
-        </is>
+      <c r="AA16" s="2" t="n">
+        <v>46129.61458333334</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
@@ -2501,10 +2475,8 @@
       <c r="Z17" t="n">
         <v>6530.25</v>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:51</t>
-        </is>
+      <c r="AA17" s="2" t="n">
+        <v>46129.78541666667</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
@@ -2623,10 +2595,8 @@
       <c r="Z18" t="n">
         <v>6530.25</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:51</t>
-        </is>
+      <c r="AA18" s="2" t="n">
+        <v>46129.78541666667</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
@@ -2745,10 +2715,8 @@
       <c r="Z19" t="n">
         <v>5415</v>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:36</t>
-        </is>
+      <c r="AA19" s="2" t="n">
+        <v>46129.775</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
@@ -2867,10 +2835,8 @@
       <c r="Z20" t="n">
         <v>5865</v>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:31</t>
-        </is>
+      <c r="AA20" s="2" t="n">
+        <v>46129.77152777778</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
@@ -2985,10 +2951,8 @@
       <c r="Z21" t="n">
         <v>609</v>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-04-18 12:34</t>
-        </is>
+      <c r="AA21" s="2" t="n">
+        <v>46130.52361111111</v>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
@@ -3103,10 +3067,8 @@
       <c r="Z22" t="n">
         <v>2254</v>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-04-18 16:25</t>
-        </is>
+      <c r="AA22" s="2" t="n">
+        <v>46130.68402777778</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
@@ -3221,10 +3183,8 @@
       <c r="Z23" t="n">
         <v>1589</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-04-18 17:16</t>
-        </is>
+      <c r="AA23" s="2" t="n">
+        <v>46130.71944444445</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
@@ -3339,10 +3299,8 @@
       <c r="Z24" t="n">
         <v>4184</v>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-04-18 20:38</t>
-        </is>
+      <c r="AA24" s="2" t="n">
+        <v>46130.85972222222</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
@@ -3461,10 +3419,8 @@
       <c r="Z25" t="n">
         <v>498.61</v>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-04-18 21:41</t>
-        </is>
+      <c r="AA25" s="2" t="n">
+        <v>46130.90347222222</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
@@ -3583,10 +3539,8 @@
       <c r="Z26" t="n">
         <v>25634</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-04-18 21:42</t>
-        </is>
+      <c r="AA26" s="2" t="n">
+        <v>46130.90416666667</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
@@ -3709,10 +3663,8 @@
       <c r="Z27" t="n">
         <v>23947</v>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-04-19 11:56</t>
-        </is>
+      <c r="AA27" s="2" t="n">
+        <v>46131.49722222222</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
@@ -3835,10 +3787,8 @@
       <c r="Z28" t="n">
         <v>5652</v>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-04-19 13:24</t>
-        </is>
+      <c r="AA28" s="2" t="n">
+        <v>46131.55833333333</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
@@ -3961,10 +3911,8 @@
       <c r="Z29" t="n">
         <v>744</v>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-04-19 14:57</t>
-        </is>
+      <c r="AA29" s="2" t="n">
+        <v>46131.62291666667</v>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
@@ -4087,10 +4035,8 @@
       <c r="Z30" t="n">
         <v>744</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-04-19 14:57</t>
-        </is>
+      <c r="AA30" s="2" t="n">
+        <v>46131.62291666667</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
@@ -4209,10 +4155,8 @@
       <c r="Z31" t="n">
         <v>1187</v>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-04-19 16:17</t>
-        </is>
+      <c r="AA31" s="2" t="n">
+        <v>46131.67847222222</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
@@ -4331,10 +4275,8 @@
       <c r="Z32" t="n">
         <v>1187</v>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-04-19 16:17</t>
-        </is>
+      <c r="AA32" s="2" t="n">
+        <v>46131.67847222222</v>
       </c>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
@@ -4449,10 +4391,8 @@
       <c r="Z33" t="n">
         <v>6019</v>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-04-19 16:49</t>
-        </is>
+      <c r="AA33" s="2" t="n">
+        <v>46131.70069444444</v>
       </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
@@ -4571,10 +4511,8 @@
       <c r="Z34" t="n">
         <v>1123</v>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-04-19 16:25</t>
-        </is>
+      <c r="AA34" s="2" t="n">
+        <v>46131.68402777778</v>
       </c>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
@@ -4697,10 +4635,8 @@
       <c r="Z35" t="n">
         <v>1123</v>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-04-19 16:25</t>
-        </is>
+      <c r="AA35" s="2" t="n">
+        <v>46131.68402777778</v>
       </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
@@ -4815,10 +4751,8 @@
       <c r="Z36" t="n">
         <v>308</v>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-04-19 21:49</t>
-        </is>
+      <c r="AA36" s="2" t="n">
+        <v>46131.90902777778</v>
       </c>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
@@ -4937,10 +4871,8 @@
       <c r="Z37" t="n">
         <v>492</v>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-04-20 09:52</t>
-        </is>
+      <c r="AA37" s="2" t="n">
+        <v>46132.41111111111</v>
       </c>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
@@ -5059,10 +4991,8 @@
       <c r="Z38" t="n">
         <v>12640</v>
       </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-04-20 10:39</t>
-        </is>
+      <c r="AA38" s="2" t="n">
+        <v>46132.44375</v>
       </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
@@ -5177,10 +5107,8 @@
       <c r="Z39" t="n">
         <v>2212</v>
       </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-04-20 11:20</t>
-        </is>
+      <c r="AA39" s="2" t="n">
+        <v>46132.47222222222</v>
       </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
@@ -5299,10 +5227,8 @@
       <c r="Z40" t="n">
         <v>20852</v>
       </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-04-20 16:19</t>
-        </is>
+      <c r="AA40" s="2" t="n">
+        <v>46132.67986111111</v>
       </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
@@ -5421,10 +5347,8 @@
       <c r="Z41" t="n">
         <v>178</v>
       </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-04-20 18:10</t>
-        </is>
+      <c r="AA41" s="2" t="n">
+        <v>46132.75694444445</v>
       </c>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
@@ -5539,10 +5463,8 @@
       <c r="Z42" t="n">
         <v>406.85</v>
       </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-04-20 21:05</t>
-        </is>
+      <c r="AA42" s="2" t="n">
+        <v>46132.87847222222</v>
       </c>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
@@ -5661,10 +5583,8 @@
       <c r="Z43" t="n">
         <v>3070.08</v>
       </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-04-20 21:48</t>
-        </is>
+      <c r="AA43" s="2" t="n">
+        <v>46132.90833333333</v>
       </c>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
@@ -5779,10 +5699,8 @@
       <c r="Z44" t="n">
         <v>2010</v>
       </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:36</t>
-        </is>
+      <c r="AA44" s="2" t="n">
+        <v>46132.94166666667</v>
       </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
@@ -5901,10 +5819,8 @@
       <c r="Z45" t="n">
         <v>574</v>
       </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-04-21 11:01</t>
-        </is>
+      <c r="AA45" s="2" t="n">
+        <v>46133.45902777778</v>
       </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
@@ -6019,10 +5935,8 @@
       <c r="Z46" t="n">
         <v>5793</v>
       </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-04-21 12:45</t>
-        </is>
+      <c r="AA46" s="2" t="n">
+        <v>46133.53125</v>
       </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
@@ -6137,10 +6051,8 @@
       <c r="Z47" t="n">
         <v>4145</v>
       </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-04-21 17:56</t>
-        </is>
+      <c r="AA47" s="2" t="n">
+        <v>46133.74722222222</v>
       </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
@@ -6259,10 +6171,8 @@
       <c r="Z48" t="n">
         <v>4693</v>
       </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-04-21 17:36</t>
-        </is>
+      <c r="AA48" s="2" t="n">
+        <v>46133.73333333333</v>
       </c>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
@@ -6377,10 +6287,8 @@
       <c r="Z49" t="n">
         <v>27674</v>
       </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-04-21 21:07</t>
-        </is>
+      <c r="AA49" s="2" t="n">
+        <v>46133.87986111111</v>
       </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
@@ -6499,10 +6407,8 @@
       <c r="Z50" t="n">
         <v>1013</v>
       </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-04-22 14:53</t>
-        </is>
+      <c r="AA50" s="2" t="n">
+        <v>46134.62013888889</v>
       </c>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
@@ -6621,10 +6527,8 @@
       <c r="Z51" t="n">
         <v>1179</v>
       </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-04-22 17:17</t>
-        </is>
+      <c r="AA51" s="2" t="n">
+        <v>46134.72013888889</v>
       </c>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
@@ -6743,10 +6647,8 @@
       <c r="Z52" t="n">
         <v>2023.25</v>
       </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-04-16 01:36</t>
-        </is>
+      <c r="AA52" s="2" t="n">
+        <v>46128.06666666667</v>
       </c>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
@@ -6861,10 +6763,8 @@
       <c r="Z53" t="n">
         <v>50724</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-04-16 10:00</t>
-        </is>
+      <c r="AA53" s="2" t="n">
+        <v>46128.41666666666</v>
       </c>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
@@ -6987,10 +6887,8 @@
       <c r="Z54" t="n">
         <v>4627</v>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-04-16 09:43</t>
-        </is>
+      <c r="AA54" s="2" t="n">
+        <v>46128.40486111111</v>
       </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
@@ -7113,10 +7011,8 @@
       <c r="Z55" t="n">
         <v>4623</v>
       </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-04-16 10:10</t>
-        </is>
+      <c r="AA55" s="2" t="n">
+        <v>46128.42361111111</v>
       </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
@@ -7239,10 +7135,8 @@
       <c r="Z56" t="n">
         <v>4620</v>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-04-16 10:12</t>
-        </is>
+      <c r="AA56" s="2" t="n">
+        <v>46128.425</v>
       </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
@@ -7361,10 +7255,8 @@
       <c r="Z57" t="n">
         <v>430</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-04-16 09:41</t>
-        </is>
+      <c r="AA57" s="2" t="n">
+        <v>46128.40347222222</v>
       </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
@@ -7483,10 +7375,8 @@
       <c r="Z58" t="n">
         <v>5337.5</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-04-16 12:03</t>
-        </is>
+      <c r="AA58" s="2" t="n">
+        <v>46128.50208333333</v>
       </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
@@ -7605,10 +7495,8 @@
       <c r="Z59" t="n">
         <v>765.79</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-04-16 11:32</t>
-        </is>
+      <c r="AA59" s="2" t="n">
+        <v>46128.48055555556</v>
       </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
@@ -7723,10 +7611,8 @@
       <c r="Z60" t="n">
         <v>419</v>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-04-16 19:23</t>
-        </is>
+      <c r="AA60" s="2" t="n">
+        <v>46128.80763888889</v>
       </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
@@ -7845,10 +7731,8 @@
       <c r="Z61" t="n">
         <v>1136.71</v>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-04-16 21:10</t>
-        </is>
+      <c r="AA61" s="2" t="n">
+        <v>46128.88194444445</v>
       </c>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
@@ -7967,10 +7851,8 @@
       <c r="Z62" t="n">
         <v>1012.25</v>
       </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-04-16 23:18</t>
-        </is>
+      <c r="AA62" s="2" t="n">
+        <v>46128.97083333333</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
@@ -8093,10 +7975,8 @@
       <c r="Z63" t="n">
         <v>940.4</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:14</t>
-        </is>
+      <c r="AA63" s="2" t="n">
+        <v>46129.34305555555</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
@@ -8215,10 +8095,8 @@
       <c r="Z64" t="n">
         <v>1188</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:47</t>
-        </is>
+      <c r="AA64" s="2" t="n">
+        <v>46129.36597222222</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="n">
@@ -8337,10 +8215,8 @@
       <c r="Z65" t="n">
         <v>1188</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:48</t>
-        </is>
+      <c r="AA65" s="2" t="n">
+        <v>46129.36666666667</v>
       </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="n">
@@ -8459,10 +8335,8 @@
       <c r="Z66" t="n">
         <v>1188</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-04-17 08:46</t>
-        </is>
+      <c r="AA66" s="2" t="n">
+        <v>46129.36527777778</v>
       </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="n">
@@ -8577,10 +8451,8 @@
       <c r="Z67" t="n">
         <v>489</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-04-17 15:41</t>
-        </is>
+      <c r="AA67" s="2" t="n">
+        <v>46129.65347222222</v>
       </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="n">
@@ -8699,10 +8571,8 @@
       <c r="Z68" t="n">
         <v>5865</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:34</t>
-        </is>
+      <c r="AA68" s="2" t="n">
+        <v>46129.77361111111</v>
       </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="n">
@@ -8817,10 +8687,8 @@
       <c r="Z69" t="n">
         <v>1675.95</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-04-17 19:12</t>
-        </is>
+      <c r="AA69" s="2" t="n">
+        <v>46129.8</v>
       </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="n">
@@ -8943,10 +8811,8 @@
       <c r="Z70" t="n">
         <v>4620</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:29</t>
-        </is>
+      <c r="AA70" s="2" t="n">
+        <v>46129.77013888889</v>
       </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="n">
@@ -9061,10 +8927,8 @@
       <c r="Z71" t="n">
         <v>2661</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:34</t>
-        </is>
+      <c r="AA71" s="2" t="n">
+        <v>46129.77361111111</v>
       </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="n">
@@ -9183,10 +9047,8 @@
       <c r="Z72" t="n">
         <v>5865</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:22</t>
-        </is>
+      <c r="AA72" s="2" t="n">
+        <v>46129.76527777778</v>
       </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="n">
@@ -9305,10 +9167,8 @@
       <c r="Z73" t="n">
         <v>5415</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:33</t>
-        </is>
+      <c r="AA73" s="2" t="n">
+        <v>46129.77291666667</v>
       </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="n">
@@ -9431,10 +9291,8 @@
       <c r="Z74" t="n">
         <v>10035</v>
       </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:57</t>
-        </is>
+      <c r="AA74" s="2" t="n">
+        <v>46129.78958333333</v>
       </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
@@ -9553,10 +9411,8 @@
       <c r="Z75" t="n">
         <v>10035</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-04-17 18:57</t>
-        </is>
+      <c r="AA75" s="2" t="n">
+        <v>46129.78958333333</v>
       </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
@@ -9675,10 +9531,8 @@
       <c r="Z76" t="n">
         <v>5139.75</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-04-17 23:14</t>
-        </is>
+      <c r="AA76" s="2" t="n">
+        <v>46129.96805555555</v>
       </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="n">
@@ -9793,10 +9647,8 @@
       <c r="Z77" t="n">
         <v>951</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-04-17 23:37</t>
-        </is>
+      <c r="AA77" s="2" t="n">
+        <v>46129.98402777778</v>
       </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="n">
@@ -9915,10 +9767,8 @@
       <c r="Z78" t="n">
         <v>457</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-04-18 16:14</t>
-        </is>
+      <c r="AA78" s="2" t="n">
+        <v>46130.67638888889</v>
       </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="n">
@@ -10037,10 +9887,8 @@
       <c r="Z79" t="n">
         <v>179</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-04-18 16:25</t>
-        </is>
+      <c r="AA79" s="2" t="n">
+        <v>46130.68402777778</v>
       </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
@@ -10155,10 +10003,8 @@
       <c r="Z80" t="n">
         <v>868</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-04-18 17:57</t>
-        </is>
+      <c r="AA80" s="2" t="n">
+        <v>46130.74791666667</v>
       </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
@@ -10277,10 +10123,8 @@
       <c r="Z81" t="n">
         <v>1166</v>
       </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-04-18 18:44</t>
-        </is>
+      <c r="AA81" s="2" t="n">
+        <v>46130.78055555555</v>
       </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="n">
@@ -10399,10 +10243,8 @@
       <c r="Z82" t="n">
         <v>283</v>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-04-18 20:43</t>
-        </is>
+      <c r="AA82" s="2" t="n">
+        <v>46130.86319444444</v>
       </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="n">
@@ -10517,10 +10359,8 @@
       <c r="Z83" t="n">
         <v>2052</v>
       </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-04-18 21:36</t>
-        </is>
+      <c r="AA83" s="2" t="n">
+        <v>46130.9</v>
       </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
@@ -10639,10 +10479,8 @@
       <c r="Z84" t="n">
         <v>6334.1</v>
       </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-04-18 22:08</t>
-        </is>
+      <c r="AA84" s="2" t="n">
+        <v>46130.92222222222</v>
       </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
@@ -10761,10 +10599,8 @@
       <c r="Z85" t="n">
         <v>55835</v>
       </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-04-19 20:57</t>
-        </is>
+      <c r="AA85" s="2" t="n">
+        <v>46131.87291666667</v>
       </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="n">
@@ -10879,10 +10715,8 @@
       <c r="Z86" t="n">
         <v>5524</v>
       </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-04-19 22:33</t>
-        </is>
+      <c r="AA86" s="2" t="n">
+        <v>46131.93958333333</v>
       </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="n">
@@ -10997,10 +10831,8 @@
       <c r="Z87" t="n">
         <v>3344</v>
       </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-04-20 09:01</t>
-        </is>
+      <c r="AA87" s="2" t="n">
+        <v>46132.37569444445</v>
       </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="n">
@@ -11119,10 +10951,8 @@
       <c r="Z88" t="n">
         <v>1545</v>
       </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-04-20 12:04</t>
-        </is>
+      <c r="AA88" s="2" t="n">
+        <v>46132.50277777778</v>
       </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="n">
@@ -11237,10 +11067,8 @@
       <c r="Z89" t="n">
         <v>664.9400000000001</v>
       </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-04-20 12:16</t>
-        </is>
+      <c r="AA89" s="2" t="n">
+        <v>46132.51111111111</v>
       </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="n">
@@ -11355,10 +11183,8 @@
       <c r="Z90" t="n">
         <v>232</v>
       </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-04-20 13:33</t>
-        </is>
+      <c r="AA90" s="2" t="n">
+        <v>46132.56458333333</v>
       </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="n">
@@ -11481,10 +11307,8 @@
       <c r="Z91" t="n">
         <v>743</v>
       </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-04-20 14:35</t>
-        </is>
+      <c r="AA91" s="2" t="n">
+        <v>46132.60763888889</v>
       </c>
       <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="n">
@@ -11607,10 +11431,8 @@
       <c r="Z92" t="n">
         <v>743</v>
       </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-04-20 14:35</t>
-        </is>
+      <c r="AA92" s="2" t="n">
+        <v>46132.60763888889</v>
       </c>
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="n">
@@ -11725,10 +11547,8 @@
       <c r="Z93" t="n">
         <v>3166</v>
       </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-04-20 14:58</t>
-        </is>
+      <c r="AA93" s="2" t="n">
+        <v>46132.62361111111</v>
       </c>
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="n">
@@ -11843,10 +11663,8 @@
       <c r="Z94" t="n">
         <v>3308</v>
       </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-04-20 14:58</t>
-        </is>
+      <c r="AA94" s="2" t="n">
+        <v>46132.62361111111</v>
       </c>
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="n">
@@ -11961,10 +11779,8 @@
       <c r="Z95" t="n">
         <v>941</v>
       </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-04-20 16:48</t>
-        </is>
+      <c r="AA95" s="2" t="n">
+        <v>46132.7</v>
       </c>
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="n">
@@ -12079,10 +11895,8 @@
       <c r="Z96" t="n">
         <v>4047</v>
       </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2026-04-20 18:22</t>
-        </is>
+      <c r="AA96" s="2" t="n">
+        <v>46132.76527777778</v>
       </c>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="n">
@@ -12201,10 +12015,8 @@
       <c r="Z97" t="n">
         <v>761</v>
       </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>2026-04-20 20:31</t>
-        </is>
+      <c r="AA97" s="2" t="n">
+        <v>46132.85486111111</v>
       </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="n">
@@ -12319,10 +12131,8 @@
       <c r="Z98" t="n">
         <v>425</v>
       </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:28</t>
-        </is>
+      <c r="AA98" s="2" t="n">
+        <v>46133.01944444444</v>
       </c>
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
@@ -12437,10 +12247,8 @@
       <c r="Z99" t="n">
         <v>5465</v>
       </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2026-04-21 08:18</t>
-        </is>
+      <c r="AA99" s="2" t="n">
+        <v>46133.34583333333</v>
       </c>
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="n">
@@ -12555,10 +12363,8 @@
       <c r="Z100" t="n">
         <v>42138</v>
       </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>2026-04-21 11:43</t>
-        </is>
+      <c r="AA100" s="2" t="n">
+        <v>46133.48819444444</v>
       </c>
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="n">
@@ -12673,10 +12479,8 @@
       <c r="Z101" t="n">
         <v>976</v>
       </c>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>2026-04-21 16:59</t>
-        </is>
+      <c r="AA101" s="2" t="n">
+        <v>46133.70763888889</v>
       </c>
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="n">
@@ -12795,10 +12599,8 @@
       <c r="Z102" t="n">
         <v>1109</v>
       </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>2026-04-21 19:59</t>
-        </is>
+      <c r="AA102" s="2" t="n">
+        <v>46133.83263888889</v>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="n">
@@ -12918,10 +12720,8 @@
       <c r="Z103" t="n">
         <v>2362</v>
       </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>2026-04-21 19:46</t>
-        </is>
+      <c r="AA103" s="2" t="n">
+        <v>46133.82361111111</v>
       </c>
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="n">
@@ -13040,10 +12840,8 @@
       <c r="Z104" t="n">
         <v>1099</v>
       </c>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>2026-04-21 21:37</t>
-        </is>
+      <c r="AA104" s="2" t="n">
+        <v>46133.90069444444</v>
       </c>
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="n">
@@ -13162,10 +12960,8 @@
       <c r="Z105" t="n">
         <v>11980</v>
       </c>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>2026-04-21 21:00</t>
-        </is>
+      <c r="AA105" s="2" t="n">
+        <v>46133.875</v>
       </c>
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="n">
@@ -13280,10 +13076,8 @@
       <c r="Z106" t="n">
         <v>768</v>
       </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>2026-04-22 08:51</t>
-        </is>
+      <c r="AA106" s="2" t="n">
+        <v>46134.36875</v>
       </c>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="n">
@@ -13406,10 +13200,8 @@
       <c r="Z107" t="n">
         <v>899</v>
       </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>2026-04-22 11:20</t>
-        </is>
+      <c r="AA107" s="2" t="n">
+        <v>46134.47222222222</v>
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="n">
@@ -13524,10 +13316,8 @@
       <c r="Z108" t="n">
         <v>4500.3</v>
       </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2026-04-22 15:50</t>
-        </is>
+      <c r="AA108" s="2" t="n">
+        <v>46134.65972222222</v>
       </c>
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="n">
@@ -13642,10 +13432,8 @@
       <c r="Z109" t="n">
         <v>2703.41</v>
       </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2026-04-22 21:04</t>
-        </is>
+      <c r="AA109" s="2" t="n">
+        <v>46134.87777777778</v>
       </c>
       <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="n">
@@ -13760,10 +13548,8 @@
       <c r="Z110" t="n">
         <v>749</v>
       </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2026-04-23 00:46</t>
-        </is>
+      <c r="AA110" s="2" t="n">
+        <v>46135.03194444445</v>
       </c>
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="n">
@@ -13878,10 +13664,8 @@
       <c r="Z111" t="n">
         <v>2038</v>
       </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>2026-04-23 07:18</t>
-        </is>
+      <c r="AA111" s="2" t="n">
+        <v>46135.30416666667</v>
       </c>
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="n">

--- a/output_test.xlsx
+++ b/output_test.xlsx
@@ -6375,7 +6375,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>มักกะสัน</t>
+          <t>ถนนเพชรบุรี</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>ประเวศ</t>
+          <t>หนองบอน</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
